--- a/r_test/plot_metrics/Plot_Metrics_Combined.xlsx
+++ b/r_test/plot_metrics/Plot_Metrics_Combined.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/patrickangst/Desktop/r_test/plot_metrics/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/patrickangst/Documents/GitHub/UWW200_Master_Thesis_public/r_test/plot_metrics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{769D12B9-93DB-594E-B728-E0E9A2AA5DA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94BD3A90-81EC-4547-B185-B6F43A5E9BBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40860" yWindow="2440" windowWidth="30100" windowHeight="13660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39860" yWindow="500" windowWidth="26400" windowHeight="19740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>Testsite</t>
   </si>
@@ -91,7 +91,52 @@
     <t>Plant_Types_MAX</t>
   </si>
   <si>
-    <t>Unique_Spectral_Species</t>
+    <t>Unique_Spectral_Species_WSS</t>
+  </si>
+  <si>
+    <t>Unique_Spectral_Species_sdbw</t>
+  </si>
+  <si>
+    <t>Unique_Spectral_Species_ratkowsky</t>
+  </si>
+  <si>
+    <t>Unique_Spectral_Species_db</t>
+  </si>
+  <si>
+    <t>Unique_Spectral_Species_sdindex</t>
+  </si>
+  <si>
+    <t>Unique_Spectral_Species_ball</t>
+  </si>
+  <si>
+    <t>Unique_Spectral_Species_tracew</t>
+  </si>
+  <si>
+    <t>Unique_Spectral_Species_friedman</t>
+  </si>
+  <si>
+    <t>Unique_Spectral_Species_rubin</t>
+  </si>
+  <si>
+    <t>Unique_Spectral_Species_pseudot2</t>
+  </si>
+  <si>
+    <t>Unique_Spectral_Species_beale</t>
+  </si>
+  <si>
+    <t>Unique_Spectral_Species_trcovw</t>
+  </si>
+  <si>
+    <t>Unique_Spectral_Species_WSS_very_Old</t>
+  </si>
+  <si>
+    <t>Unique_Spectral_Species_WSS_old</t>
+  </si>
+  <si>
+    <t>Unique_Spectral_Species_WSS_ds</t>
+  </si>
+  <si>
+    <t>Unique_Spectral_Species_WSS_50</t>
   </si>
 </sst>
 </file>
@@ -444,7 +489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:Z14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
@@ -457,10 +502,25 @@
     <col min="8" max="8" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.83203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="33.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="28" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="29" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="26" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="26.1640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="27.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -494,8 +554,53 @@
       <c r="K1" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="L1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -527,10 +632,55 @@
         <v>28</v>
       </c>
       <c r="K2">
+        <v>23</v>
+      </c>
+      <c r="L2">
+        <v>23</v>
+      </c>
+      <c r="M2">
+        <v>34</v>
+      </c>
+      <c r="N2">
+        <v>35</v>
+      </c>
+      <c r="O2">
         <v>22</v>
       </c>
+      <c r="P2">
+        <v>4</v>
+      </c>
+      <c r="Q2">
+        <v>46</v>
+      </c>
+      <c r="R2">
+        <v>2</v>
+      </c>
+      <c r="S2">
+        <v>4</v>
+      </c>
+      <c r="T2">
+        <v>3</v>
+      </c>
+      <c r="U2">
+        <v>3</v>
+      </c>
+      <c r="V2">
+        <v>39</v>
+      </c>
+      <c r="W2">
+        <v>39</v>
+      </c>
+      <c r="X2">
+        <v>3</v>
+      </c>
+      <c r="Y2">
+        <v>2</v>
+      </c>
+      <c r="Z2">
+        <v>3</v>
+      </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -562,10 +712,55 @@
         <v>28</v>
       </c>
       <c r="K3">
+        <v>23</v>
+      </c>
+      <c r="L3">
+        <v>5</v>
+      </c>
+      <c r="M3">
+        <v>45</v>
+      </c>
+      <c r="N3">
+        <v>42</v>
+      </c>
+      <c r="O3">
         <v>19</v>
       </c>
+      <c r="P3">
+        <v>4</v>
+      </c>
+      <c r="Q3">
+        <v>45</v>
+      </c>
+      <c r="R3">
+        <v>4</v>
+      </c>
+      <c r="S3">
+        <v>6</v>
+      </c>
+      <c r="T3">
+        <v>3</v>
+      </c>
+      <c r="U3">
+        <v>3</v>
+      </c>
+      <c r="V3">
+        <v>8</v>
+      </c>
+      <c r="W3">
+        <v>6</v>
+      </c>
+      <c r="X3">
+        <v>3</v>
+      </c>
+      <c r="Y3">
+        <v>3</v>
+      </c>
+      <c r="Z3">
+        <v>3</v>
+      </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -597,10 +792,55 @@
         <v>50</v>
       </c>
       <c r="K4">
+        <v>85</v>
+      </c>
+      <c r="L4">
+        <v>11</v>
+      </c>
+      <c r="M4">
+        <v>49</v>
+      </c>
+      <c r="N4">
+        <v>34</v>
+      </c>
+      <c r="O4">
         <v>36</v>
       </c>
+      <c r="P4">
+        <v>6</v>
+      </c>
+      <c r="Q4">
+        <v>50</v>
+      </c>
+      <c r="R4">
+        <v>2</v>
+      </c>
+      <c r="S4">
+        <v>4</v>
+      </c>
+      <c r="T4">
+        <v>3</v>
+      </c>
+      <c r="U4">
+        <v>3</v>
+      </c>
+      <c r="V4">
+        <v>38</v>
+      </c>
+      <c r="W4">
+        <v>35</v>
+      </c>
+      <c r="X4">
+        <v>2</v>
+      </c>
+      <c r="Y4">
+        <v>2</v>
+      </c>
+      <c r="Z4">
+        <v>3</v>
+      </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -632,10 +872,55 @@
         <v>40</v>
       </c>
       <c r="K5">
+        <v>18</v>
+      </c>
+      <c r="L5">
         <v>17</v>
       </c>
+      <c r="M5">
+        <v>26</v>
+      </c>
+      <c r="N5">
+        <v>9</v>
+      </c>
+      <c r="O5">
+        <v>17</v>
+      </c>
+      <c r="P5">
+        <v>5</v>
+      </c>
+      <c r="Q5">
+        <v>50</v>
+      </c>
+      <c r="R5">
+        <v>2</v>
+      </c>
+      <c r="S5">
+        <v>5</v>
+      </c>
+      <c r="T5">
+        <v>3</v>
+      </c>
+      <c r="U5">
+        <v>3</v>
+      </c>
+      <c r="V5">
+        <v>20</v>
+      </c>
+      <c r="W5">
+        <v>17</v>
+      </c>
+      <c r="X5">
+        <v>2</v>
+      </c>
+      <c r="Y5">
+        <v>2</v>
+      </c>
+      <c r="Z5">
+        <v>3</v>
+      </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -667,10 +952,55 @@
         <v>25</v>
       </c>
       <c r="K6">
+        <v>36</v>
+      </c>
+      <c r="L6">
+        <v>33</v>
+      </c>
+      <c r="M6">
+        <v>40</v>
+      </c>
+      <c r="N6">
+        <v>46</v>
+      </c>
+      <c r="O6">
         <v>45</v>
       </c>
+      <c r="P6">
+        <v>6</v>
+      </c>
+      <c r="Q6">
+        <v>48</v>
+      </c>
+      <c r="R6">
+        <v>2</v>
+      </c>
+      <c r="S6">
+        <v>3</v>
+      </c>
+      <c r="T6">
+        <v>3</v>
+      </c>
+      <c r="U6">
+        <v>3</v>
+      </c>
+      <c r="V6">
+        <v>5</v>
+      </c>
+      <c r="W6">
+        <v>3</v>
+      </c>
+      <c r="X6">
+        <v>3</v>
+      </c>
+      <c r="Y6">
+        <v>2</v>
+      </c>
+      <c r="Z6">
+        <v>3</v>
+      </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -702,10 +1032,55 @@
         <v>20</v>
       </c>
       <c r="K7">
+        <v>15</v>
+      </c>
+      <c r="L7">
+        <v>48</v>
+      </c>
+      <c r="M7">
+        <v>5</v>
+      </c>
+      <c r="N7">
+        <v>49</v>
+      </c>
+      <c r="O7">
         <v>11</v>
       </c>
+      <c r="P7">
+        <v>5</v>
+      </c>
+      <c r="Q7">
+        <v>50</v>
+      </c>
+      <c r="R7">
+        <v>2</v>
+      </c>
+      <c r="S7">
+        <v>8</v>
+      </c>
+      <c r="T7">
+        <v>3</v>
+      </c>
+      <c r="U7">
+        <v>3</v>
+      </c>
+      <c r="V7">
+        <v>15</v>
+      </c>
+      <c r="W7">
+        <v>32</v>
+      </c>
+      <c r="X7">
+        <v>2</v>
+      </c>
+      <c r="Y7">
+        <v>2</v>
+      </c>
+      <c r="Z7">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -737,10 +1112,55 @@
         <v>20</v>
       </c>
       <c r="K8">
+        <v>20</v>
+      </c>
+      <c r="L8">
+        <v>21</v>
+      </c>
+      <c r="M8">
+        <v>41</v>
+      </c>
+      <c r="N8">
+        <v>25</v>
+      </c>
+      <c r="O8">
         <v>43</v>
       </c>
+      <c r="P8">
+        <v>6</v>
+      </c>
+      <c r="Q8">
+        <v>48</v>
+      </c>
+      <c r="R8">
+        <v>2</v>
+      </c>
+      <c r="S8">
+        <v>3</v>
+      </c>
+      <c r="T8">
+        <v>3</v>
+      </c>
+      <c r="U8">
+        <v>3</v>
+      </c>
+      <c r="V8">
+        <v>5</v>
+      </c>
+      <c r="W8">
+        <v>48</v>
+      </c>
+      <c r="X8">
+        <v>3</v>
+      </c>
+      <c r="Y8">
+        <v>2</v>
+      </c>
+      <c r="Z8">
+        <v>3</v>
+      </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -774,8 +1194,53 @@
       <c r="K9">
         <v>6</v>
       </c>
+      <c r="L9">
+        <v>51</v>
+      </c>
+      <c r="M9">
+        <v>11</v>
+      </c>
+      <c r="N9">
+        <v>29</v>
+      </c>
+      <c r="O9">
+        <v>6</v>
+      </c>
+      <c r="P9">
+        <v>12</v>
+      </c>
+      <c r="Q9">
+        <v>50</v>
+      </c>
+      <c r="R9">
+        <v>2</v>
+      </c>
+      <c r="S9">
+        <v>8</v>
+      </c>
+      <c r="T9">
+        <v>3</v>
+      </c>
+      <c r="U9">
+        <v>3</v>
+      </c>
+      <c r="V9">
+        <v>42</v>
+      </c>
+      <c r="W9">
+        <v>14</v>
+      </c>
+      <c r="X9">
+        <v>2</v>
+      </c>
+      <c r="Y9">
+        <v>2</v>
+      </c>
+      <c r="Z9">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -807,10 +1272,55 @@
         <v>23</v>
       </c>
       <c r="K10">
+        <v>37</v>
+      </c>
+      <c r="L10">
+        <v>29</v>
+      </c>
+      <c r="M10">
+        <v>11</v>
+      </c>
+      <c r="N10">
+        <v>10</v>
+      </c>
+      <c r="O10">
         <v>19</v>
       </c>
+      <c r="P10">
+        <v>3</v>
+      </c>
+      <c r="Q10">
+        <v>50</v>
+      </c>
+      <c r="R10">
+        <v>20</v>
+      </c>
+      <c r="S10">
+        <v>9</v>
+      </c>
+      <c r="T10">
+        <v>3</v>
+      </c>
+      <c r="U10">
+        <v>3</v>
+      </c>
+      <c r="V10">
+        <v>39</v>
+      </c>
+      <c r="W10">
+        <v>40</v>
+      </c>
+      <c r="X10">
+        <v>2</v>
+      </c>
+      <c r="Y10">
+        <v>2</v>
+      </c>
+      <c r="Z10">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -842,10 +1352,55 @@
         <v>41</v>
       </c>
       <c r="K11">
+        <v>42</v>
+      </c>
+      <c r="L11">
+        <v>43</v>
+      </c>
+      <c r="M11">
+        <v>25</v>
+      </c>
+      <c r="N11">
+        <v>47</v>
+      </c>
+      <c r="O11">
         <v>11</v>
       </c>
+      <c r="P11">
+        <v>4</v>
+      </c>
+      <c r="Q11">
+        <v>50</v>
+      </c>
+      <c r="R11">
+        <v>3</v>
+      </c>
+      <c r="S11">
+        <v>10</v>
+      </c>
+      <c r="T11">
+        <v>3</v>
+      </c>
+      <c r="U11">
+        <v>3</v>
+      </c>
+      <c r="V11">
+        <v>4</v>
+      </c>
+      <c r="W11">
+        <v>41</v>
+      </c>
+      <c r="X11">
+        <v>3</v>
+      </c>
+      <c r="Y11">
+        <v>2</v>
+      </c>
+      <c r="Z11">
+        <v>3</v>
+      </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -877,10 +1432,55 @@
         <v>52</v>
       </c>
       <c r="K12">
+        <v>58</v>
+      </c>
+      <c r="L12">
+        <v>37</v>
+      </c>
+      <c r="M12">
+        <v>10</v>
+      </c>
+      <c r="N12">
+        <v>15</v>
+      </c>
+      <c r="O12">
         <v>32</v>
       </c>
+      <c r="P12">
+        <v>3</v>
+      </c>
+      <c r="Q12">
+        <v>50</v>
+      </c>
+      <c r="R12">
+        <v>2</v>
+      </c>
+      <c r="S12">
+        <v>8</v>
+      </c>
+      <c r="T12">
+        <v>3</v>
+      </c>
+      <c r="U12">
+        <v>3</v>
+      </c>
+      <c r="V12">
+        <v>42</v>
+      </c>
+      <c r="W12">
+        <v>37</v>
+      </c>
+      <c r="X12">
+        <v>3</v>
+      </c>
+      <c r="Y12">
+        <v>3</v>
+      </c>
+      <c r="Z12">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -912,10 +1512,55 @@
         <v>21</v>
       </c>
       <c r="K13">
+        <v>21</v>
+      </c>
+      <c r="L13">
+        <v>21</v>
+      </c>
+      <c r="M13">
+        <v>39</v>
+      </c>
+      <c r="N13">
+        <v>39</v>
+      </c>
+      <c r="O13">
         <v>44</v>
       </c>
+      <c r="P13">
+        <v>6</v>
+      </c>
+      <c r="Q13">
+        <v>50</v>
+      </c>
+      <c r="R13">
+        <v>2</v>
+      </c>
+      <c r="S13">
+        <v>4</v>
+      </c>
+      <c r="T13">
+        <v>3</v>
+      </c>
+      <c r="U13">
+        <v>4</v>
+      </c>
+      <c r="V13">
+        <v>44</v>
+      </c>
+      <c r="W13">
+        <v>40</v>
+      </c>
+      <c r="X13">
+        <v>2</v>
+      </c>
+      <c r="Y13">
+        <v>2</v>
+      </c>
+      <c r="Z13">
+        <v>4</v>
+      </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -947,7 +1592,52 @@
         <v>24</v>
       </c>
       <c r="K14">
+        <v>87</v>
+      </c>
+      <c r="L14">
+        <v>29</v>
+      </c>
+      <c r="M14">
+        <v>39</v>
+      </c>
+      <c r="N14">
+        <v>37</v>
+      </c>
+      <c r="O14">
         <v>47</v>
+      </c>
+      <c r="P14">
+        <v>4</v>
+      </c>
+      <c r="Q14">
+        <v>50</v>
+      </c>
+      <c r="R14">
+        <v>2</v>
+      </c>
+      <c r="S14">
+        <v>5</v>
+      </c>
+      <c r="T14">
+        <v>3</v>
+      </c>
+      <c r="U14">
+        <v>3</v>
+      </c>
+      <c r="V14">
+        <v>16</v>
+      </c>
+      <c r="W14">
+        <v>16</v>
+      </c>
+      <c r="X14">
+        <v>2</v>
+      </c>
+      <c r="Y14">
+        <v>2</v>
+      </c>
+      <c r="Z14">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/r_test/plot_metrics/Plot_Metrics_Combined.xlsx
+++ b/r_test/plot_metrics/Plot_Metrics_Combined.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/patrickangst/Documents/GitHub/UWW200_Master_Thesis_public/r_test/plot_metrics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94BD3A90-81EC-4547-B185-B6F43A5E9BBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8DE0226-74A0-E545-B71D-C7324DC2B072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39860" yWindow="500" windowWidth="26400" windowHeight="19740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1000" yWindow="760" windowWidth="26400" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>Testsite</t>
   </si>
@@ -137,6 +137,9 @@
   </si>
   <si>
     <t>Unique_Spectral_Species_WSS_50</t>
+  </si>
+  <si>
+    <t>Unique_Spectral_Species_WSS_100</t>
   </si>
 </sst>
 </file>
@@ -489,7 +492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z14"/>
+  <dimension ref="A1:AA14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
@@ -503,24 +506,25 @@
     <col min="9" max="9" width="14.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="25.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="28.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="27.83203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="33.1640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="25.83203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="23.83203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="28" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="29" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="26" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="26.1640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="29.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="27.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="33.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="28" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="26" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="26.1640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="27.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -555,52 +559,55 @@
         <v>23</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -638,49 +645,52 @@
         <v>23</v>
       </c>
       <c r="M2">
+        <v>23</v>
+      </c>
+      <c r="N2">
         <v>34</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>35</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>22</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>4</v>
       </c>
-      <c r="Q2">
+      <c r="R2">
         <v>46</v>
       </c>
-      <c r="R2">
-        <v>2</v>
-      </c>
       <c r="S2">
+        <v>2</v>
+      </c>
+      <c r="T2">
         <v>4</v>
       </c>
-      <c r="T2">
-        <v>3</v>
-      </c>
       <c r="U2">
         <v>3</v>
       </c>
       <c r="V2">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="W2">
         <v>39</v>
       </c>
       <c r="X2">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="Y2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z2">
+        <v>2</v>
+      </c>
+      <c r="AA2">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -712,55 +722,58 @@
         <v>28</v>
       </c>
       <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3">
         <v>23</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>5</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>45</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>42</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>19</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>4</v>
       </c>
-      <c r="Q3">
+      <c r="R3">
         <v>45</v>
       </c>
-      <c r="R3">
+      <c r="S3">
         <v>4</v>
       </c>
-      <c r="S3">
+      <c r="T3">
         <v>6</v>
       </c>
-      <c r="T3">
-        <v>3</v>
-      </c>
       <c r="U3">
         <v>3</v>
       </c>
       <c r="V3">
+        <v>3</v>
+      </c>
+      <c r="W3">
         <v>8</v>
       </c>
-      <c r="W3">
+      <c r="X3">
         <v>6</v>
       </c>
-      <c r="X3">
-        <v>3</v>
-      </c>
       <c r="Y3">
         <v>3</v>
       </c>
       <c r="Z3">
         <v>3</v>
       </c>
+      <c r="AA3">
+        <v>3</v>
+      </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -792,55 +805,58 @@
         <v>50</v>
       </c>
       <c r="K4">
+        <v>11</v>
+      </c>
+      <c r="L4">
         <v>85</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>11</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>49</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>34</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>36</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>6</v>
       </c>
-      <c r="Q4">
+      <c r="R4">
         <v>50</v>
       </c>
-      <c r="R4">
-        <v>2</v>
-      </c>
       <c r="S4">
+        <v>2</v>
+      </c>
+      <c r="T4">
         <v>4</v>
       </c>
-      <c r="T4">
-        <v>3</v>
-      </c>
       <c r="U4">
         <v>3</v>
       </c>
       <c r="V4">
+        <v>3</v>
+      </c>
+      <c r="W4">
         <v>38</v>
       </c>
-      <c r="W4">
+      <c r="X4">
         <v>35</v>
       </c>
-      <c r="X4">
-        <v>2</v>
-      </c>
       <c r="Y4">
         <v>2</v>
       </c>
       <c r="Z4">
+        <v>2</v>
+      </c>
+      <c r="AA4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -872,55 +888,58 @@
         <v>40</v>
       </c>
       <c r="K5">
+        <v>17</v>
+      </c>
+      <c r="L5">
         <v>18</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>17</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>26</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>9</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>17</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <v>5</v>
       </c>
-      <c r="Q5">
+      <c r="R5">
         <v>50</v>
       </c>
-      <c r="R5">
-        <v>2</v>
-      </c>
       <c r="S5">
+        <v>2</v>
+      </c>
+      <c r="T5">
         <v>5</v>
       </c>
-      <c r="T5">
-        <v>3</v>
-      </c>
       <c r="U5">
         <v>3</v>
       </c>
       <c r="V5">
+        <v>3</v>
+      </c>
+      <c r="W5">
         <v>20</v>
       </c>
-      <c r="W5">
+      <c r="X5">
         <v>17</v>
       </c>
-      <c r="X5">
-        <v>2</v>
-      </c>
       <c r="Y5">
         <v>2</v>
       </c>
       <c r="Z5">
+        <v>2</v>
+      </c>
+      <c r="AA5">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -952,31 +971,31 @@
         <v>25</v>
       </c>
       <c r="K6">
+        <v>33</v>
+      </c>
+      <c r="L6">
         <v>36</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>33</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>40</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>46</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>45</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
         <v>6</v>
       </c>
-      <c r="Q6">
+      <c r="R6">
         <v>48</v>
       </c>
-      <c r="R6">
-        <v>2</v>
-      </c>
       <c r="S6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T6">
         <v>3</v>
@@ -985,22 +1004,25 @@
         <v>3</v>
       </c>
       <c r="V6">
+        <v>3</v>
+      </c>
+      <c r="W6">
         <v>5</v>
       </c>
-      <c r="W6">
-        <v>3</v>
-      </c>
       <c r="X6">
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z6">
+        <v>2</v>
+      </c>
+      <c r="AA6">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1032,55 +1054,58 @@
         <v>20</v>
       </c>
       <c r="K7">
+        <v>48</v>
+      </c>
+      <c r="L7">
         <v>15</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>48</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>5</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>49</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>11</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>5</v>
       </c>
-      <c r="Q7">
+      <c r="R7">
         <v>50</v>
       </c>
-      <c r="R7">
-        <v>2</v>
-      </c>
       <c r="S7">
+        <v>2</v>
+      </c>
+      <c r="T7">
         <v>8</v>
       </c>
-      <c r="T7">
-        <v>3</v>
-      </c>
       <c r="U7">
         <v>3</v>
       </c>
       <c r="V7">
+        <v>3</v>
+      </c>
+      <c r="W7">
         <v>15</v>
       </c>
-      <c r="W7">
+      <c r="X7">
         <v>32</v>
       </c>
-      <c r="X7">
-        <v>2</v>
-      </c>
       <c r="Y7">
         <v>2</v>
       </c>
       <c r="Z7">
+        <v>2</v>
+      </c>
+      <c r="AA7">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -1112,31 +1137,31 @@
         <v>20</v>
       </c>
       <c r="K8">
+        <v>21</v>
+      </c>
+      <c r="L8">
         <v>20</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>21</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>41</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>25</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>43</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <v>6</v>
       </c>
-      <c r="Q8">
+      <c r="R8">
         <v>48</v>
       </c>
-      <c r="R8">
-        <v>2</v>
-      </c>
       <c r="S8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T8">
         <v>3</v>
@@ -1145,22 +1170,25 @@
         <v>3</v>
       </c>
       <c r="V8">
+        <v>3</v>
+      </c>
+      <c r="W8">
         <v>5</v>
       </c>
-      <c r="W8">
+      <c r="X8">
         <v>48</v>
       </c>
-      <c r="X8">
-        <v>3</v>
-      </c>
       <c r="Y8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z8">
+        <v>2</v>
+      </c>
+      <c r="AA8">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -1192,55 +1220,58 @@
         <v>20</v>
       </c>
       <c r="K9">
+        <v>50</v>
+      </c>
+      <c r="L9">
         <v>6</v>
       </c>
-      <c r="L9">
-        <v>51</v>
-      </c>
       <c r="M9">
+        <v>50</v>
+      </c>
+      <c r="N9">
         <v>11</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>29</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>6</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <v>12</v>
       </c>
-      <c r="Q9">
+      <c r="R9">
         <v>50</v>
       </c>
-      <c r="R9">
-        <v>2</v>
-      </c>
       <c r="S9">
+        <v>2</v>
+      </c>
+      <c r="T9">
         <v>8</v>
       </c>
-      <c r="T9">
-        <v>3</v>
-      </c>
       <c r="U9">
         <v>3</v>
       </c>
       <c r="V9">
+        <v>3</v>
+      </c>
+      <c r="W9">
         <v>42</v>
       </c>
-      <c r="W9">
+      <c r="X9">
         <v>14</v>
       </c>
-      <c r="X9">
-        <v>2</v>
-      </c>
       <c r="Y9">
         <v>2</v>
       </c>
       <c r="Z9">
+        <v>2</v>
+      </c>
+      <c r="AA9">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -1272,55 +1303,58 @@
         <v>23</v>
       </c>
       <c r="K10">
+        <v>29</v>
+      </c>
+      <c r="L10">
         <v>37</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>29</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>11</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>10</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>19</v>
       </c>
-      <c r="P10">
-        <v>3</v>
-      </c>
       <c r="Q10">
+        <v>3</v>
+      </c>
+      <c r="R10">
         <v>50</v>
       </c>
-      <c r="R10">
+      <c r="S10">
         <v>20</v>
       </c>
-      <c r="S10">
+      <c r="T10">
         <v>9</v>
       </c>
-      <c r="T10">
-        <v>3</v>
-      </c>
       <c r="U10">
         <v>3</v>
       </c>
       <c r="V10">
+        <v>3</v>
+      </c>
+      <c r="W10">
         <v>39</v>
       </c>
-      <c r="W10">
+      <c r="X10">
         <v>40</v>
       </c>
-      <c r="X10">
-        <v>2</v>
-      </c>
       <c r="Y10">
         <v>2</v>
       </c>
       <c r="Z10">
+        <v>2</v>
+      </c>
+      <c r="AA10">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -1352,55 +1386,58 @@
         <v>41</v>
       </c>
       <c r="K11">
+        <v>43</v>
+      </c>
+      <c r="L11">
         <v>42</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>43</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>25</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>47</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>11</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>4</v>
       </c>
-      <c r="Q11">
+      <c r="R11">
         <v>50</v>
       </c>
-      <c r="R11">
-        <v>3</v>
-      </c>
       <c r="S11">
+        <v>3</v>
+      </c>
+      <c r="T11">
         <v>10</v>
       </c>
-      <c r="T11">
-        <v>3</v>
-      </c>
       <c r="U11">
         <v>3</v>
       </c>
       <c r="V11">
+        <v>3</v>
+      </c>
+      <c r="W11">
         <v>4</v>
       </c>
-      <c r="W11">
+      <c r="X11">
         <v>41</v>
       </c>
-      <c r="X11">
-        <v>3</v>
-      </c>
       <c r="Y11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z11">
+        <v>2</v>
+      </c>
+      <c r="AA11">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -1432,55 +1469,58 @@
         <v>52</v>
       </c>
       <c r="K12">
+        <v>37</v>
+      </c>
+      <c r="L12">
         <v>58</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>37</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>10</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>15</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>32</v>
       </c>
-      <c r="P12">
-        <v>3</v>
-      </c>
       <c r="Q12">
+        <v>3</v>
+      </c>
+      <c r="R12">
         <v>50</v>
       </c>
-      <c r="R12">
-        <v>2</v>
-      </c>
       <c r="S12">
+        <v>2</v>
+      </c>
+      <c r="T12">
         <v>8</v>
       </c>
-      <c r="T12">
-        <v>3</v>
-      </c>
       <c r="U12">
         <v>3</v>
       </c>
       <c r="V12">
+        <v>3</v>
+      </c>
+      <c r="W12">
         <v>42</v>
       </c>
-      <c r="W12">
+      <c r="X12">
         <v>37</v>
       </c>
-      <c r="X12">
-        <v>3</v>
-      </c>
       <c r="Y12">
         <v>3</v>
       </c>
       <c r="Z12">
         <v>3</v>
       </c>
+      <c r="AA12">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -1518,49 +1558,52 @@
         <v>21</v>
       </c>
       <c r="M13">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="N13">
         <v>39</v>
       </c>
       <c r="O13">
+        <v>39</v>
+      </c>
+      <c r="P13">
         <v>44</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>6</v>
       </c>
-      <c r="Q13">
+      <c r="R13">
         <v>50</v>
       </c>
-      <c r="R13">
-        <v>2</v>
-      </c>
       <c r="S13">
+        <v>2</v>
+      </c>
+      <c r="T13">
         <v>4</v>
       </c>
-      <c r="T13">
-        <v>3</v>
-      </c>
       <c r="U13">
+        <v>3</v>
+      </c>
+      <c r="V13">
         <v>4</v>
       </c>
-      <c r="V13">
+      <c r="W13">
         <v>44</v>
       </c>
-      <c r="W13">
+      <c r="X13">
         <v>40</v>
       </c>
-      <c r="X13">
-        <v>2</v>
-      </c>
       <c r="Y13">
         <v>2</v>
       </c>
       <c r="Z13">
+        <v>2</v>
+      </c>
+      <c r="AA13">
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -1592,51 +1635,54 @@
         <v>24</v>
       </c>
       <c r="K14">
+        <v>29</v>
+      </c>
+      <c r="L14">
         <v>87</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>29</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>39</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>37</v>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>47</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>4</v>
       </c>
-      <c r="Q14">
+      <c r="R14">
         <v>50</v>
       </c>
-      <c r="R14">
-        <v>2</v>
-      </c>
       <c r="S14">
+        <v>2</v>
+      </c>
+      <c r="T14">
         <v>5</v>
       </c>
-      <c r="T14">
-        <v>3</v>
-      </c>
       <c r="U14">
         <v>3</v>
       </c>
       <c r="V14">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="W14">
         <v>16</v>
       </c>
       <c r="X14">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="Y14">
         <v>2</v>
       </c>
       <c r="Z14">
+        <v>2</v>
+      </c>
+      <c r="AA14">
         <v>3</v>
       </c>
     </row>

--- a/r_test/plot_metrics/Plot_Metrics_Combined.xlsx
+++ b/r_test/plot_metrics/Plot_Metrics_Combined.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/patrickangst/Documents/GitHub/UWW200_Master_Thesis_public/r_test/plot_metrics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8DE0226-74A0-E545-B71D-C7324DC2B072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F76D3BD1-CABC-5341-A84D-B1612E83022C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1000" yWindow="760" windowWidth="26400" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19740" yWindow="760" windowWidth="14820" windowHeight="20580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -163,12 +163,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -183,11 +189,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -561,7 +571,7 @@
       <c r="L1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>38</v>
       </c>
       <c r="N1" s="1" t="s">
@@ -639,12 +649,12 @@
         <v>28</v>
       </c>
       <c r="K2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L2">
         <v>23</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="3">
         <v>23</v>
       </c>
       <c r="N2">
@@ -722,12 +732,12 @@
         <v>28</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="L3">
         <v>23</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="3">
         <v>5</v>
       </c>
       <c r="N3">
@@ -805,12 +815,12 @@
         <v>50</v>
       </c>
       <c r="K4">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="L4">
         <v>85</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="3">
         <v>11</v>
       </c>
       <c r="N4">
@@ -888,12 +898,12 @@
         <v>40</v>
       </c>
       <c r="K5">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L5">
         <v>18</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="3">
         <v>17</v>
       </c>
       <c r="N5">
@@ -971,12 +981,12 @@
         <v>25</v>
       </c>
       <c r="K6">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L6">
         <v>36</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="3">
         <v>33</v>
       </c>
       <c r="N6">
@@ -1054,12 +1064,12 @@
         <v>20</v>
       </c>
       <c r="K7">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L7">
         <v>15</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="3">
         <v>48</v>
       </c>
       <c r="N7">
@@ -1137,12 +1147,12 @@
         <v>20</v>
       </c>
       <c r="K8">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="L8">
         <v>20</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="3">
         <v>21</v>
       </c>
       <c r="N8">
@@ -1220,12 +1230,12 @@
         <v>20</v>
       </c>
       <c r="K9">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="L9">
         <v>6</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="3">
         <v>50</v>
       </c>
       <c r="N9">
@@ -1308,7 +1318,7 @@
       <c r="L10">
         <v>37</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="3">
         <v>29</v>
       </c>
       <c r="N10">
@@ -1386,12 +1396,12 @@
         <v>41</v>
       </c>
       <c r="K11">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="L11">
         <v>42</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="3">
         <v>43</v>
       </c>
       <c r="N11">
@@ -1469,12 +1479,12 @@
         <v>52</v>
       </c>
       <c r="K12">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L12">
         <v>58</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="3">
         <v>37</v>
       </c>
       <c r="N12">
@@ -1552,12 +1562,12 @@
         <v>21</v>
       </c>
       <c r="K13">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="L13">
         <v>21</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="3">
         <v>21</v>
       </c>
       <c r="N13">
@@ -1635,12 +1645,12 @@
         <v>24</v>
       </c>
       <c r="K14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L14">
         <v>87</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="3">
         <v>29</v>
       </c>
       <c r="N14">

--- a/r_test/plot_metrics/Plot_Metrics_Combined.xlsx
+++ b/r_test/plot_metrics/Plot_Metrics_Combined.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/patrickangst/Documents/GitHub/UWW200_Master_Thesis_public/r_test/plot_metrics/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patri\Documents\GitHub\UWW200_Master_Thesis_public\r_test\plot_metrics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F76D3BD1-CABC-5341-A84D-B1612E83022C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD8390CC-FD74-4CD9-B345-5BAD663D9831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19740" yWindow="760" windowWidth="14820" windowHeight="20580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1270" yWindow="5680" windowWidth="37220" windowHeight="15290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>Testsite</t>
   </si>
@@ -91,9 +104,6 @@
     <t>Plant_Types_MAX</t>
   </si>
   <si>
-    <t>Unique_Spectral_Species_WSS</t>
-  </si>
-  <si>
     <t>Unique_Spectral_Species_sdbw</t>
   </si>
   <si>
@@ -127,19 +137,7 @@
     <t>Unique_Spectral_Species_trcovw</t>
   </si>
   <si>
-    <t>Unique_Spectral_Species_WSS_very_Old</t>
-  </si>
-  <si>
-    <t>Unique_Spectral_Species_WSS_old</t>
-  </si>
-  <si>
-    <t>Unique_Spectral_Species_WSS_ds</t>
-  </si>
-  <si>
-    <t>Unique_Spectral_Species_WSS_50</t>
-  </si>
-  <si>
-    <t>Unique_Spectral_Species_WSS_100</t>
+    <t>Unique_Spectral_Species_WCSS</t>
   </si>
 </sst>
 </file>
@@ -163,18 +161,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -189,15 +181,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -502,39 +490,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:V14"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="28.1640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="27.83203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="33.1640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="25.83203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="23.83203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="28" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="26" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="26.1640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.6328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="31.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="25.1796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="29.54296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="26" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="28.7265625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="30.7265625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="27.453125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="31" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="28.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -566,58 +549,43 @@
         <v>22</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="N1" s="1" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AA1" s="1" t="s">
-        <v>34</v>
-      </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -649,58 +617,43 @@
         <v>28</v>
       </c>
       <c r="K2">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="L2">
-        <v>23</v>
-      </c>
-      <c r="M2" s="3">
-        <v>23</v>
+        <v>4</v>
+      </c>
+      <c r="M2">
+        <v>46</v>
       </c>
       <c r="N2">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="O2">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="P2">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="Q2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R2">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="S2">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="T2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V2">
         <v>3</v>
       </c>
-      <c r="W2">
-        <v>39</v>
-      </c>
-      <c r="X2">
-        <v>39</v>
-      </c>
-      <c r="Y2">
-        <v>3</v>
-      </c>
-      <c r="Z2">
-        <v>2</v>
-      </c>
-      <c r="AA2">
-        <v>3</v>
-      </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -732,34 +685,34 @@
         <v>28</v>
       </c>
       <c r="K3">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="L3">
-        <v>23</v>
-      </c>
-      <c r="M3" s="3">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>45</v>
       </c>
       <c r="N3">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="O3">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="P3">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="Q3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R3">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="S3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U3">
         <v>3</v>
@@ -767,23 +720,8 @@
       <c r="V3">
         <v>3</v>
       </c>
-      <c r="W3">
-        <v>8</v>
-      </c>
-      <c r="X3">
-        <v>6</v>
-      </c>
-      <c r="Y3">
-        <v>3</v>
-      </c>
-      <c r="Z3">
-        <v>3</v>
-      </c>
-      <c r="AA3">
-        <v>3</v>
-      </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -815,58 +753,43 @@
         <v>50</v>
       </c>
       <c r="K4">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="L4">
-        <v>85</v>
-      </c>
-      <c r="M4" s="3">
-        <v>11</v>
+        <v>6</v>
+      </c>
+      <c r="M4">
+        <v>50</v>
       </c>
       <c r="N4">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="O4">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="P4">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="Q4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R4">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="S4">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="T4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V4">
         <v>3</v>
       </c>
-      <c r="W4">
-        <v>38</v>
-      </c>
-      <c r="X4">
-        <v>35</v>
-      </c>
-      <c r="Y4">
-        <v>2</v>
-      </c>
-      <c r="Z4">
-        <v>2</v>
-      </c>
-      <c r="AA4">
-        <v>3</v>
-      </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -898,58 +821,43 @@
         <v>40</v>
       </c>
       <c r="K5">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="L5">
-        <v>18</v>
-      </c>
-      <c r="M5" s="3">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>50</v>
+      </c>
+      <c r="N5">
+        <v>2</v>
+      </c>
+      <c r="O5">
+        <v>5</v>
+      </c>
+      <c r="P5">
+        <v>3</v>
+      </c>
+      <c r="Q5">
+        <v>3</v>
+      </c>
+      <c r="R5">
+        <v>20</v>
+      </c>
+      <c r="S5">
         <v>17</v>
       </c>
-      <c r="N5">
-        <v>26</v>
-      </c>
-      <c r="O5">
-        <v>9</v>
-      </c>
-      <c r="P5">
-        <v>17</v>
-      </c>
-      <c r="Q5">
-        <v>5</v>
-      </c>
-      <c r="R5">
-        <v>50</v>
-      </c>
-      <c r="S5">
-        <v>2</v>
-      </c>
       <c r="T5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V5">
         <v>3</v>
       </c>
-      <c r="W5">
-        <v>20</v>
-      </c>
-      <c r="X5">
-        <v>17</v>
-      </c>
-      <c r="Y5">
-        <v>2</v>
-      </c>
-      <c r="Z5">
-        <v>2</v>
-      </c>
-      <c r="AA5">
-        <v>3</v>
-      </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -981,58 +889,43 @@
         <v>25</v>
       </c>
       <c r="K6">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="L6">
-        <v>36</v>
-      </c>
-      <c r="M6" s="3">
-        <v>33</v>
+        <v>6</v>
+      </c>
+      <c r="M6">
+        <v>48</v>
       </c>
       <c r="N6">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="O6">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="P6">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="Q6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R6">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="S6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T6">
         <v>3</v>
       </c>
       <c r="U6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V6">
         <v>3</v>
       </c>
-      <c r="W6">
-        <v>5</v>
-      </c>
-      <c r="X6">
-        <v>3</v>
-      </c>
-      <c r="Y6">
-        <v>3</v>
-      </c>
-      <c r="Z6">
-        <v>2</v>
-      </c>
-      <c r="AA6">
-        <v>3</v>
-      </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1064,58 +957,43 @@
         <v>20</v>
       </c>
       <c r="K7">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="L7">
+        <v>5</v>
+      </c>
+      <c r="M7">
+        <v>50</v>
+      </c>
+      <c r="N7">
+        <v>2</v>
+      </c>
+      <c r="O7">
+        <v>8</v>
+      </c>
+      <c r="P7">
+        <v>3</v>
+      </c>
+      <c r="Q7">
+        <v>3</v>
+      </c>
+      <c r="R7">
         <v>15</v>
       </c>
-      <c r="M7" s="3">
-        <v>48</v>
-      </c>
-      <c r="N7">
-        <v>5</v>
-      </c>
-      <c r="O7">
-        <v>49</v>
-      </c>
-      <c r="P7">
-        <v>11</v>
-      </c>
-      <c r="Q7">
-        <v>5</v>
-      </c>
-      <c r="R7">
-        <v>50</v>
-      </c>
       <c r="S7">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="T7">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V7">
         <v>3</v>
       </c>
-      <c r="W7">
-        <v>15</v>
-      </c>
-      <c r="X7">
-        <v>32</v>
-      </c>
-      <c r="Y7">
-        <v>2</v>
-      </c>
-      <c r="Z7">
-        <v>2</v>
-      </c>
-      <c r="AA7">
-        <v>3</v>
-      </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -1147,58 +1025,43 @@
         <v>20</v>
       </c>
       <c r="K8">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="L8">
-        <v>20</v>
-      </c>
-      <c r="M8" s="3">
-        <v>21</v>
+        <v>6</v>
+      </c>
+      <c r="M8">
+        <v>48</v>
       </c>
       <c r="N8">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="O8">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="P8">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="Q8">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R8">
+        <v>5</v>
+      </c>
+      <c r="S8">
         <v>48</v>
       </c>
-      <c r="S8">
-        <v>2</v>
-      </c>
       <c r="T8">
         <v>3</v>
       </c>
       <c r="U8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V8">
         <v>3</v>
       </c>
-      <c r="W8">
-        <v>5</v>
-      </c>
-      <c r="X8">
-        <v>48</v>
-      </c>
-      <c r="Y8">
-        <v>3</v>
-      </c>
-      <c r="Z8">
-        <v>2</v>
-      </c>
-      <c r="AA8">
-        <v>3</v>
-      </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -1230,58 +1093,43 @@
         <v>20</v>
       </c>
       <c r="K9">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="L9">
-        <v>6</v>
-      </c>
-      <c r="M9" s="3">
+        <v>12</v>
+      </c>
+      <c r="M9">
         <v>50</v>
       </c>
       <c r="N9">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="O9">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="P9">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q9">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="R9">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="S9">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="T9">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V9">
         <v>3</v>
       </c>
-      <c r="W9">
-        <v>42</v>
-      </c>
-      <c r="X9">
-        <v>14</v>
-      </c>
-      <c r="Y9">
-        <v>2</v>
-      </c>
-      <c r="Z9">
-        <v>2</v>
-      </c>
-      <c r="AA9">
-        <v>3</v>
-      </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -1313,58 +1161,43 @@
         <v>23</v>
       </c>
       <c r="K10">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="L10">
-        <v>37</v>
-      </c>
-      <c r="M10" s="3">
-        <v>29</v>
+        <v>3</v>
+      </c>
+      <c r="M10">
+        <v>50</v>
       </c>
       <c r="N10">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="O10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P10">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="Q10">
         <v>3</v>
       </c>
       <c r="R10">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="S10">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="T10">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V10">
         <v>3</v>
       </c>
-      <c r="W10">
-        <v>39</v>
-      </c>
-      <c r="X10">
-        <v>40</v>
-      </c>
-      <c r="Y10">
-        <v>2</v>
-      </c>
-      <c r="Z10">
-        <v>2</v>
-      </c>
-      <c r="AA10">
-        <v>3</v>
-      </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -1399,55 +1232,40 @@
         <v>48</v>
       </c>
       <c r="L11">
-        <v>42</v>
-      </c>
-      <c r="M11" s="3">
-        <v>43</v>
+        <v>4</v>
+      </c>
+      <c r="M11">
+        <v>50</v>
       </c>
       <c r="N11">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="O11">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="P11">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="Q11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R11">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="S11">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="T11">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="U11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V11">
         <v>3</v>
       </c>
-      <c r="W11">
-        <v>4</v>
-      </c>
-      <c r="X11">
-        <v>41</v>
-      </c>
-      <c r="Y11">
-        <v>3</v>
-      </c>
-      <c r="Z11">
-        <v>2</v>
-      </c>
-      <c r="AA11">
-        <v>3</v>
-      </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -1479,34 +1297,34 @@
         <v>52</v>
       </c>
       <c r="K12">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="L12">
-        <v>58</v>
-      </c>
-      <c r="M12" s="3">
+        <v>3</v>
+      </c>
+      <c r="M12">
+        <v>50</v>
+      </c>
+      <c r="N12">
+        <v>2</v>
+      </c>
+      <c r="O12">
+        <v>8</v>
+      </c>
+      <c r="P12">
+        <v>3</v>
+      </c>
+      <c r="Q12">
+        <v>3</v>
+      </c>
+      <c r="R12">
+        <v>42</v>
+      </c>
+      <c r="S12">
         <v>37</v>
       </c>
-      <c r="N12">
-        <v>10</v>
-      </c>
-      <c r="O12">
-        <v>15</v>
-      </c>
-      <c r="P12">
-        <v>32</v>
-      </c>
-      <c r="Q12">
-        <v>3</v>
-      </c>
-      <c r="R12">
-        <v>50</v>
-      </c>
-      <c r="S12">
-        <v>2</v>
-      </c>
       <c r="T12">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U12">
         <v>3</v>
@@ -1514,23 +1332,8 @@
       <c r="V12">
         <v>3</v>
       </c>
-      <c r="W12">
-        <v>42</v>
-      </c>
-      <c r="X12">
-        <v>37</v>
-      </c>
-      <c r="Y12">
-        <v>3</v>
-      </c>
-      <c r="Z12">
-        <v>3</v>
-      </c>
-      <c r="AA12">
-        <v>3</v>
-      </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -1562,58 +1365,43 @@
         <v>21</v>
       </c>
       <c r="K13">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L13">
-        <v>21</v>
-      </c>
-      <c r="M13" s="3">
-        <v>21</v>
+        <v>6</v>
+      </c>
+      <c r="M13">
+        <v>50</v>
       </c>
       <c r="N13">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="O13">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="P13">
+        <v>3</v>
+      </c>
+      <c r="Q13">
+        <v>4</v>
+      </c>
+      <c r="R13">
         <v>44</v>
       </c>
-      <c r="Q13">
-        <v>6</v>
-      </c>
-      <c r="R13">
-        <v>50</v>
-      </c>
       <c r="S13">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="T13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V13">
         <v>4</v>
       </c>
-      <c r="W13">
-        <v>44</v>
-      </c>
-      <c r="X13">
-        <v>40</v>
-      </c>
-      <c r="Y13">
-        <v>2</v>
-      </c>
-      <c r="Z13">
-        <v>2</v>
-      </c>
-      <c r="AA13">
-        <v>4</v>
-      </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -1645,54 +1433,39 @@
         <v>24</v>
       </c>
       <c r="K14">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="L14">
-        <v>87</v>
-      </c>
-      <c r="M14" s="3">
-        <v>29</v>
+        <v>4</v>
+      </c>
+      <c r="M14">
+        <v>50</v>
       </c>
       <c r="N14">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="O14">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="P14">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="Q14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R14">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="S14">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="T14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V14">
-        <v>3</v>
-      </c>
-      <c r="W14">
-        <v>16</v>
-      </c>
-      <c r="X14">
-        <v>16</v>
-      </c>
-      <c r="Y14">
-        <v>2</v>
-      </c>
-      <c r="Z14">
-        <v>2</v>
-      </c>
-      <c r="AA14">
         <v>3</v>
       </c>
     </row>

--- a/r_test/plot_metrics/Plot_Metrics_Combined.xlsx
+++ b/r_test/plot_metrics/Plot_Metrics_Combined.xlsx
@@ -8,12 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patri\Documents\GitHub\UWW200_Master_Thesis_public\r_test\plot_metrics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD8390CC-FD74-4CD9-B345-5BAD663D9831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E9773C-CC3C-4915-A7CA-D96F51AB84D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1270" yWindow="5680" windowWidth="37220" windowHeight="15290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4070" yWindow="3200" windowWidth="32950" windowHeight="14300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="part_c_d" sheetId="3" r:id="rId2"/>
+    <sheet name="part_e" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="39">
   <si>
     <t>Testsite</t>
   </si>
@@ -138,6 +141,18 @@
   </si>
   <si>
     <t>Unique_Spectral_Species_WCSS</t>
+  </si>
+  <si>
+    <t>Unique plant cummunities</t>
+  </si>
+  <si>
+    <t>Unique habitat types</t>
+  </si>
+  <si>
+    <t>Unique plant species</t>
+  </si>
+  <si>
+    <t>Unique spectral species</t>
   </si>
 </sst>
 </file>
@@ -493,28 +508,28 @@
   <dimension ref="A1:V14"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.6328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.6328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26.6328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="31.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="27.453125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="25.1796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="29.54296875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="26" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="28.7265625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="30.7265625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="27.453125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="31" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="27.54296875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="28.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.90625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="28.08984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="31.90625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.6328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="25.36328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="29.81640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="26.26953125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="30.90625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="27.6328125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="31.1796875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.35">
@@ -1472,4 +1487,550 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4CB34EE-4F67-4477-8FF9-41D97ADB11AC}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2">
+        <v>9</v>
+      </c>
+      <c r="C2">
+        <v>7</v>
+      </c>
+      <c r="D2">
+        <v>142</v>
+      </c>
+      <c r="E2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3">
+        <v>12</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>73</v>
+      </c>
+      <c r="E3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4">
+        <v>16</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>51</v>
+      </c>
+      <c r="E4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>51</v>
+      </c>
+      <c r="E5">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6">
+        <v>17</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>46</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>44</v>
+      </c>
+      <c r="E7">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>88</v>
+      </c>
+      <c r="E8">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9">
+        <v>6</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9">
+        <v>133</v>
+      </c>
+      <c r="E9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10">
+        <v>8</v>
+      </c>
+      <c r="C10">
+        <v>5</v>
+      </c>
+      <c r="D10">
+        <v>46</v>
+      </c>
+      <c r="E10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11">
+        <v>5</v>
+      </c>
+      <c r="D11">
+        <v>58</v>
+      </c>
+      <c r="E11">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1939FA77-8242-4C4C-B69D-486772391B8B}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>6</v>
+      </c>
+      <c r="D2">
+        <v>79</v>
+      </c>
+      <c r="E2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>68</v>
+      </c>
+      <c r="E3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4">
+        <v>9</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>41</v>
+      </c>
+      <c r="E4">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A12AF84-08F5-4C76-AE94-97BBFC97A09B}">
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>6</v>
+      </c>
+      <c r="D2">
+        <v>79</v>
+      </c>
+      <c r="E2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>68</v>
+      </c>
+      <c r="E3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4">
+        <v>9</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+      <c r="D4">
+        <v>142</v>
+      </c>
+      <c r="E4">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5">
+        <v>12</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>73</v>
+      </c>
+      <c r="E5">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6">
+        <v>16</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>51</v>
+      </c>
+      <c r="E6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>51</v>
+      </c>
+      <c r="E7">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8">
+        <v>17</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8">
+        <v>46</v>
+      </c>
+      <c r="E8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9">
+        <v>9</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>44</v>
+      </c>
+      <c r="E9">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>41</v>
+      </c>
+      <c r="E10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11">
+        <v>3</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11">
+        <v>88</v>
+      </c>
+      <c r="E11">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12">
+        <v>6</v>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12">
+        <v>133</v>
+      </c>
+      <c r="E12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13">
+        <v>8</v>
+      </c>
+      <c r="C13">
+        <v>5</v>
+      </c>
+      <c r="D13">
+        <v>46</v>
+      </c>
+      <c r="E13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14">
+        <v>10</v>
+      </c>
+      <c r="C14">
+        <v>5</v>
+      </c>
+      <c r="D14">
+        <v>58</v>
+      </c>
+      <c r="E14">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/r_test/plot_metrics/Plot_Metrics_Combined.xlsx
+++ b/r_test/plot_metrics/Plot_Metrics_Combined.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10526"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patri\Documents\GitHub\UWW200_Master_Thesis_public\r_test\plot_metrics\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/patrickangst/Documents/GitHub/UWW200_Master_Thesis_public/r_test/plot_metrics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E9773C-CC3C-4915-A7CA-D96F51AB84D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{957A706A-7A0B-D14C-A95A-569367744E8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4070" yWindow="3200" windowWidth="32950" windowHeight="14300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4080" yWindow="3200" windowWidth="32960" windowHeight="14300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -56,9 +56,6 @@
     <t>simpson_index_TAX</t>
   </si>
   <si>
-    <t>Unique_Plant_Types</t>
-  </si>
-  <si>
     <t>AN_TJ_1</t>
   </si>
   <si>
@@ -153,6 +150,9 @@
   </si>
   <si>
     <t>Unique spectral species</t>
+  </si>
+  <si>
+    <t>Unique_Plant_Species</t>
   </si>
 </sst>
 </file>
@@ -506,33 +506,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V14"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.26953125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="28.08984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="31.90625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="27.6328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="25.36328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="29.81640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="26.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="31.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="29.83203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="26.33203125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="30.90625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="27.6328125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="31.1796875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="30.83203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="31.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="27.83203125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -552,57 +551,57 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>7</v>
       </c>
       <c r="B2">
         <v>0.74</v>
@@ -668,9 +667,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0.72</v>
@@ -736,9 +735,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0.84693877551020402</v>
@@ -804,9 +803,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0.90541781450872361</v>
@@ -872,9 +871,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6">
         <v>0.92881944444444442</v>
@@ -940,9 +939,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7">
         <v>0.67500000000000004</v>
@@ -1008,9 +1007,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8">
         <v>0.9211111111111111</v>
@@ -1076,9 +1075,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>0.86444444444444446</v>
@@ -1144,9 +1143,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B10">
         <v>0.83111111111111113</v>
@@ -1212,9 +1211,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B11">
         <v>0.66</v>
@@ -1280,9 +1279,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12">
         <v>0.77562326869806097</v>
@@ -1348,9 +1347,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13">
         <v>0.85440000000000005</v>
@@ -1416,9 +1415,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B14">
         <v>0.89417360285374559</v>
@@ -1492,17 +1491,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4CB34EE-4F67-4477-8FF9-41D97ADB11AC}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1513,15 +1512,15 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2">
         <v>9</v>
@@ -1536,9 +1535,9 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>12</v>
@@ -1553,9 +1552,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>16</v>
@@ -1570,9 +1569,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -1587,9 +1586,9 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6">
         <v>17</v>
@@ -1604,9 +1603,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7">
         <v>9</v>
@@ -1621,9 +1620,9 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8">
         <v>3</v>
@@ -1638,9 +1637,9 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9">
         <v>6</v>
@@ -1655,9 +1654,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10">
         <v>8</v>
@@ -1672,9 +1671,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -1697,16 +1696,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1939FA77-8242-4C4C-B69D-486772391B8B}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1717,15 +1716,15 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>7</v>
       </c>
       <c r="B2">
         <v>4</v>
@@ -1740,9 +1739,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>4</v>
@@ -1757,9 +1756,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <v>9</v>
@@ -1782,35 +1781,35 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A12AF84-08F5-4C76-AE94-97BBFC97A09B}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2">
         <v>4</v>
@@ -1825,9 +1824,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>4</v>
@@ -1842,9 +1841,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>9</v>
@@ -1859,9 +1858,9 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>12</v>
@@ -1876,9 +1875,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6">
         <v>16</v>
@@ -1893,9 +1892,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7">
         <v>4</v>
@@ -1910,9 +1909,9 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8">
         <v>17</v>
@@ -1927,9 +1926,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>9</v>
@@ -1944,9 +1943,9 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B10">
         <v>9</v>
@@ -1961,9 +1960,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B11">
         <v>3</v>
@@ -1978,9 +1977,9 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12">
         <v>6</v>
@@ -1995,9 +1994,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13">
         <v>8</v>
@@ -2012,9 +2011,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B14">
         <v>10</v>

--- a/r_test/plot_metrics/Plot_Metrics_Combined.xlsx
+++ b/r_test/plot_metrics/Plot_Metrics_Combined.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/patrickangst/Documents/GitHub/UWW200_Master_Thesis_public/r_test/plot_metrics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{957A706A-7A0B-D14C-A95A-569367744E8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8D0FCD6-7371-B241-BF72-AC844E9D03D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4080" yWindow="3200" windowWidth="32960" windowHeight="14300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57680" yWindow="500" windowWidth="18980" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="42">
   <si>
     <t>Testsite</t>
   </si>
@@ -153,6 +153,15 @@
   </si>
   <si>
     <t>Unique_Plant_Species</t>
+  </si>
+  <si>
+    <t>Unique_Habitat_Types_Short1</t>
+  </si>
+  <si>
+    <t>Unique_Habitat_Types_Short2</t>
+  </si>
+  <si>
+    <t>Unique_Habitat_Types_Short3</t>
   </si>
 </sst>
 </file>
@@ -505,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:Y14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.83203125" bestFit="1" customWidth="1"/>
@@ -513,25 +522,27 @@
     <col min="3" max="3" width="24.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="28.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="31.83203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="25.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="29.83203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="26.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="30.83203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="31.1640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="27.83203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="24.83203125" customWidth="1"/>
+    <col min="9" max="9" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="31.83203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="29.83203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="30.83203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="31.1640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="27.83203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -548,58 +559,67 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -616,58 +636,67 @@
         <v>6</v>
       </c>
       <c r="F2">
+        <v>4</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
         <v>0.96497934234954441</v>
       </c>
-      <c r="G2">
+      <c r="J2">
         <v>79</v>
       </c>
-      <c r="H2">
+      <c r="K2">
         <v>13.8</v>
       </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
         <v>28</v>
       </c>
-      <c r="K2">
+      <c r="N2">
         <v>26</v>
       </c>
-      <c r="L2">
-        <v>4</v>
-      </c>
-      <c r="M2">
+      <c r="O2">
+        <v>4</v>
+      </c>
+      <c r="P2">
         <v>46</v>
       </c>
-      <c r="N2">
-        <v>2</v>
-      </c>
-      <c r="O2">
-        <v>4</v>
-      </c>
-      <c r="P2">
-        <v>3</v>
-      </c>
       <c r="Q2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R2">
+        <v>4</v>
+      </c>
+      <c r="S2">
+        <v>3</v>
+      </c>
+      <c r="T2">
+        <v>3</v>
+      </c>
+      <c r="U2">
         <v>39</v>
       </c>
-      <c r="S2">
+      <c r="V2">
         <v>39</v>
       </c>
-      <c r="T2">
-        <v>3</v>
-      </c>
-      <c r="U2">
-        <v>2</v>
-      </c>
-      <c r="V2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W2">
+        <v>3</v>
+      </c>
+      <c r="X2">
+        <v>2</v>
+      </c>
+      <c r="Y2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -684,58 +713,67 @@
         <v>3</v>
       </c>
       <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
         <v>0.90904848905157309</v>
       </c>
-      <c r="G3">
+      <c r="J3">
         <v>68</v>
       </c>
-      <c r="H3">
+      <c r="K3">
         <v>19.8</v>
       </c>
-      <c r="I3">
+      <c r="L3">
         <v>10</v>
       </c>
-      <c r="J3">
+      <c r="M3">
         <v>28</v>
       </c>
-      <c r="K3">
+      <c r="N3">
         <v>12</v>
       </c>
-      <c r="L3">
-        <v>4</v>
-      </c>
-      <c r="M3">
+      <c r="O3">
+        <v>4</v>
+      </c>
+      <c r="P3">
         <v>45</v>
       </c>
-      <c r="N3">
-        <v>4</v>
-      </c>
-      <c r="O3">
+      <c r="Q3">
+        <v>4</v>
+      </c>
+      <c r="R3">
         <v>6</v>
       </c>
-      <c r="P3">
-        <v>3</v>
-      </c>
-      <c r="Q3">
-        <v>3</v>
-      </c>
-      <c r="R3">
+      <c r="S3">
+        <v>3</v>
+      </c>
+      <c r="T3">
+        <v>3</v>
+      </c>
+      <c r="U3">
         <v>8</v>
       </c>
-      <c r="S3">
+      <c r="V3">
         <v>6</v>
       </c>
-      <c r="T3">
-        <v>3</v>
-      </c>
-      <c r="U3">
-        <v>3</v>
-      </c>
-      <c r="V3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W3">
+        <v>3</v>
+      </c>
+      <c r="X3">
+        <v>3</v>
+      </c>
+      <c r="Y3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -752,58 +790,67 @@
         <v>7</v>
       </c>
       <c r="F4">
+        <v>7</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
         <v>0.95519617590265793</v>
       </c>
-      <c r="G4">
+      <c r="J4">
         <v>142</v>
       </c>
-      <c r="H4">
+      <c r="K4">
         <v>33.607142857142897</v>
       </c>
-      <c r="I4">
+      <c r="L4">
         <v>15</v>
-      </c>
-      <c r="J4">
-        <v>50</v>
-      </c>
-      <c r="K4">
-        <v>43</v>
-      </c>
-      <c r="L4">
-        <v>6</v>
       </c>
       <c r="M4">
         <v>50</v>
       </c>
       <c r="N4">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="O4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P4">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="Q4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R4">
+        <v>4</v>
+      </c>
+      <c r="S4">
+        <v>3</v>
+      </c>
+      <c r="T4">
+        <v>3</v>
+      </c>
+      <c r="U4">
         <v>38</v>
       </c>
-      <c r="S4">
+      <c r="V4">
         <v>35</v>
       </c>
-      <c r="T4">
-        <v>2</v>
-      </c>
-      <c r="U4">
-        <v>2</v>
-      </c>
-      <c r="V4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W4">
+        <v>2</v>
+      </c>
+      <c r="X4">
+        <v>2</v>
+      </c>
+      <c r="Y4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -820,58 +867,67 @@
         <v>4</v>
       </c>
       <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
         <v>0.88310662145401841</v>
       </c>
-      <c r="G5">
+      <c r="J5">
         <v>73</v>
       </c>
-      <c r="H5">
+      <c r="K5">
         <v>22.545454545454501</v>
       </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
         <v>40</v>
       </c>
-      <c r="K5">
+      <c r="N5">
         <v>40</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>50</v>
-      </c>
-      <c r="N5">
-        <v>2</v>
       </c>
       <c r="O5">
         <v>5</v>
       </c>
       <c r="P5">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="Q5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R5">
+        <v>5</v>
+      </c>
+      <c r="S5">
+        <v>3</v>
+      </c>
+      <c r="T5">
+        <v>3</v>
+      </c>
+      <c r="U5">
         <v>20</v>
       </c>
-      <c r="S5">
+      <c r="V5">
         <v>17</v>
       </c>
-      <c r="T5">
-        <v>2</v>
-      </c>
-      <c r="U5">
-        <v>2</v>
-      </c>
-      <c r="V5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W5">
+        <v>2</v>
+      </c>
+      <c r="X5">
+        <v>2</v>
+      </c>
+      <c r="Y5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -888,58 +944,67 @@
         <v>3</v>
       </c>
       <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
         <v>0.91472311604002332</v>
       </c>
-      <c r="G6">
+      <c r="J6">
         <v>51</v>
       </c>
-      <c r="H6">
+      <c r="K6">
         <v>14</v>
       </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6">
         <v>25</v>
       </c>
-      <c r="K6">
+      <c r="N6">
         <v>25</v>
       </c>
-      <c r="L6">
+      <c r="O6">
         <v>6</v>
       </c>
-      <c r="M6">
+      <c r="P6">
         <v>48</v>
       </c>
-      <c r="N6">
-        <v>2</v>
-      </c>
-      <c r="O6">
-        <v>3</v>
-      </c>
-      <c r="P6">
-        <v>3</v>
-      </c>
       <c r="Q6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R6">
+        <v>3</v>
+      </c>
+      <c r="S6">
+        <v>3</v>
+      </c>
+      <c r="T6">
+        <v>3</v>
+      </c>
+      <c r="U6">
         <v>5</v>
       </c>
-      <c r="S6">
-        <v>3</v>
-      </c>
-      <c r="T6">
-        <v>3</v>
-      </c>
-      <c r="U6">
-        <v>2</v>
-      </c>
       <c r="V6">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W6">
+        <v>3</v>
+      </c>
+      <c r="X6">
+        <v>2</v>
+      </c>
+      <c r="Y6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -956,58 +1021,67 @@
         <v>3</v>
       </c>
       <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7">
         <v>0.9252539517364966</v>
       </c>
-      <c r="G7">
+      <c r="J7">
         <v>51</v>
       </c>
-      <c r="H7">
+      <c r="K7">
         <v>11.65</v>
       </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
-      <c r="J7">
+      <c r="L7">
+        <v>3</v>
+      </c>
+      <c r="M7">
         <v>20</v>
       </c>
-      <c r="K7">
+      <c r="N7">
         <v>27</v>
       </c>
-      <c r="L7">
+      <c r="O7">
         <v>5</v>
       </c>
-      <c r="M7">
+      <c r="P7">
         <v>50</v>
       </c>
-      <c r="N7">
-        <v>2</v>
-      </c>
-      <c r="O7">
+      <c r="Q7">
+        <v>2</v>
+      </c>
+      <c r="R7">
         <v>8</v>
       </c>
-      <c r="P7">
-        <v>3</v>
-      </c>
-      <c r="Q7">
-        <v>3</v>
-      </c>
-      <c r="R7">
+      <c r="S7">
+        <v>3</v>
+      </c>
+      <c r="T7">
+        <v>3</v>
+      </c>
+      <c r="U7">
         <v>15</v>
       </c>
-      <c r="S7">
+      <c r="V7">
         <v>32</v>
       </c>
-      <c r="T7">
-        <v>2</v>
-      </c>
-      <c r="U7">
-        <v>2</v>
-      </c>
-      <c r="V7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7">
+        <v>2</v>
+      </c>
+      <c r="X7">
+        <v>2</v>
+      </c>
+      <c r="Y7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1024,58 +1098,67 @@
         <v>3</v>
       </c>
       <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
         <v>0.86642272172683299</v>
       </c>
-      <c r="G8">
+      <c r="J8">
         <v>46</v>
       </c>
-      <c r="H8">
+      <c r="K8">
         <v>9.15</v>
       </c>
-      <c r="I8">
+      <c r="L8">
         <v>1</v>
       </c>
-      <c r="J8">
+      <c r="M8">
         <v>20</v>
       </c>
-      <c r="K8">
+      <c r="N8">
         <v>11</v>
       </c>
-      <c r="L8">
+      <c r="O8">
         <v>6</v>
       </c>
-      <c r="M8">
+      <c r="P8">
         <v>48</v>
       </c>
-      <c r="N8">
-        <v>2</v>
-      </c>
-      <c r="O8">
-        <v>3</v>
-      </c>
-      <c r="P8">
-        <v>3</v>
-      </c>
       <c r="Q8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R8">
+        <v>3</v>
+      </c>
+      <c r="S8">
+        <v>3</v>
+      </c>
+      <c r="T8">
+        <v>3</v>
+      </c>
+      <c r="U8">
         <v>5</v>
       </c>
-      <c r="S8">
+      <c r="V8">
         <v>48</v>
       </c>
-      <c r="T8">
-        <v>3</v>
-      </c>
-      <c r="U8">
-        <v>2</v>
-      </c>
-      <c r="V8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8">
+        <v>3</v>
+      </c>
+      <c r="X8">
+        <v>2</v>
+      </c>
+      <c r="Y8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -1092,58 +1175,67 @@
         <v>2</v>
       </c>
       <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
         <v>0.89782865967441328</v>
       </c>
-      <c r="G9">
+      <c r="J9">
         <v>44</v>
       </c>
-      <c r="H9">
+      <c r="K9">
         <v>12.533333333333299</v>
       </c>
-      <c r="I9">
-        <v>2</v>
-      </c>
-      <c r="J9">
+      <c r="L9">
+        <v>2</v>
+      </c>
+      <c r="M9">
         <v>20</v>
       </c>
-      <c r="K9">
+      <c r="N9">
         <v>27</v>
       </c>
-      <c r="L9">
+      <c r="O9">
         <v>12</v>
       </c>
-      <c r="M9">
+      <c r="P9">
         <v>50</v>
       </c>
-      <c r="N9">
-        <v>2</v>
-      </c>
-      <c r="O9">
+      <c r="Q9">
+        <v>2</v>
+      </c>
+      <c r="R9">
         <v>8</v>
       </c>
-      <c r="P9">
-        <v>3</v>
-      </c>
-      <c r="Q9">
-        <v>3</v>
-      </c>
-      <c r="R9">
+      <c r="S9">
+        <v>3</v>
+      </c>
+      <c r="T9">
+        <v>3</v>
+      </c>
+      <c r="U9">
         <v>42</v>
       </c>
-      <c r="S9">
+      <c r="V9">
         <v>14</v>
       </c>
-      <c r="T9">
-        <v>2</v>
-      </c>
-      <c r="U9">
-        <v>2</v>
-      </c>
-      <c r="V9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9">
+        <v>2</v>
+      </c>
+      <c r="X9">
+        <v>2</v>
+      </c>
+      <c r="Y9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1160,58 +1252,67 @@
         <v>2</v>
       </c>
       <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
         <v>0.8931422666857739</v>
       </c>
-      <c r="G10">
+      <c r="J10">
         <v>41</v>
       </c>
-      <c r="H10">
+      <c r="K10">
         <v>10.9</v>
       </c>
-      <c r="I10">
+      <c r="L10">
         <v>5</v>
       </c>
-      <c r="J10">
+      <c r="M10">
         <v>23</v>
       </c>
-      <c r="K10">
+      <c r="N10">
         <v>7</v>
       </c>
-      <c r="L10">
-        <v>3</v>
-      </c>
-      <c r="M10">
+      <c r="O10">
+        <v>3</v>
+      </c>
+      <c r="P10">
         <v>50</v>
       </c>
-      <c r="N10">
+      <c r="Q10">
         <v>20</v>
       </c>
-      <c r="O10">
+      <c r="R10">
         <v>9</v>
       </c>
-      <c r="P10">
-        <v>3</v>
-      </c>
-      <c r="Q10">
-        <v>3</v>
-      </c>
-      <c r="R10">
+      <c r="S10">
+        <v>3</v>
+      </c>
+      <c r="T10">
+        <v>3</v>
+      </c>
+      <c r="U10">
         <v>39</v>
       </c>
-      <c r="S10">
+      <c r="V10">
         <v>40</v>
       </c>
-      <c r="T10">
-        <v>2</v>
-      </c>
-      <c r="U10">
-        <v>2</v>
-      </c>
-      <c r="V10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10">
+        <v>2</v>
+      </c>
+      <c r="X10">
+        <v>2</v>
+      </c>
+      <c r="Y10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -1228,58 +1329,67 @@
         <v>2</v>
       </c>
       <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
         <v>0.94679029336145426</v>
       </c>
-      <c r="G11">
+      <c r="J11">
         <v>88</v>
       </c>
-      <c r="H11">
+      <c r="K11">
         <v>32.200000000000003</v>
       </c>
-      <c r="I11">
+      <c r="L11">
         <v>27</v>
       </c>
-      <c r="J11">
+      <c r="M11">
         <v>41</v>
       </c>
-      <c r="K11">
+      <c r="N11">
         <v>48</v>
       </c>
-      <c r="L11">
-        <v>4</v>
-      </c>
-      <c r="M11">
+      <c r="O11">
+        <v>4</v>
+      </c>
+      <c r="P11">
         <v>50</v>
       </c>
-      <c r="N11">
-        <v>3</v>
-      </c>
-      <c r="O11">
+      <c r="Q11">
+        <v>3</v>
+      </c>
+      <c r="R11">
         <v>10</v>
       </c>
-      <c r="P11">
-        <v>3</v>
-      </c>
-      <c r="Q11">
-        <v>3</v>
-      </c>
-      <c r="R11">
-        <v>4</v>
-      </c>
       <c r="S11">
+        <v>3</v>
+      </c>
+      <c r="T11">
+        <v>3</v>
+      </c>
+      <c r="U11">
+        <v>4</v>
+      </c>
+      <c r="V11">
         <v>41</v>
       </c>
-      <c r="T11">
-        <v>3</v>
-      </c>
-      <c r="U11">
-        <v>2</v>
-      </c>
-      <c r="V11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11">
+        <v>3</v>
+      </c>
+      <c r="X11">
+        <v>2</v>
+      </c>
+      <c r="Y11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -1296,58 +1406,67 @@
         <v>3</v>
       </c>
       <c r="F12">
+        <v>3</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="H12">
+        <v>2</v>
+      </c>
+      <c r="I12">
         <v>0.95245067939365846</v>
       </c>
-      <c r="G12">
+      <c r="J12">
         <v>133</v>
       </c>
-      <c r="H12">
+      <c r="K12">
         <v>34.526315789473699</v>
       </c>
-      <c r="I12">
+      <c r="L12">
         <v>12</v>
       </c>
-      <c r="J12">
+      <c r="M12">
         <v>52</v>
       </c>
-      <c r="K12">
+      <c r="N12">
         <v>5</v>
       </c>
-      <c r="L12">
-        <v>3</v>
-      </c>
-      <c r="M12">
+      <c r="O12">
+        <v>3</v>
+      </c>
+      <c r="P12">
         <v>50</v>
       </c>
-      <c r="N12">
-        <v>2</v>
-      </c>
-      <c r="O12">
+      <c r="Q12">
+        <v>2</v>
+      </c>
+      <c r="R12">
         <v>8</v>
       </c>
-      <c r="P12">
-        <v>3</v>
-      </c>
-      <c r="Q12">
-        <v>3</v>
-      </c>
-      <c r="R12">
+      <c r="S12">
+        <v>3</v>
+      </c>
+      <c r="T12">
+        <v>3</v>
+      </c>
+      <c r="U12">
         <v>42</v>
       </c>
-      <c r="S12">
+      <c r="V12">
         <v>37</v>
       </c>
-      <c r="T12">
-        <v>3</v>
-      </c>
-      <c r="U12">
-        <v>3</v>
-      </c>
-      <c r="V12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12">
+        <v>3</v>
+      </c>
+      <c r="X12">
+        <v>3</v>
+      </c>
+      <c r="Y12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -1364,58 +1483,67 @@
         <v>5</v>
       </c>
       <c r="F13">
+        <v>3</v>
+      </c>
+      <c r="G13">
+        <v>3</v>
+      </c>
+      <c r="H13">
+        <v>2</v>
+      </c>
+      <c r="I13">
         <v>0.7820992039879664</v>
       </c>
-      <c r="G13">
+      <c r="J13">
         <v>46</v>
       </c>
-      <c r="H13">
+      <c r="K13">
         <v>7.5185185185185199</v>
       </c>
-      <c r="I13">
+      <c r="L13">
         <v>0</v>
       </c>
-      <c r="J13">
+      <c r="M13">
         <v>21</v>
       </c>
-      <c r="K13">
+      <c r="N13">
         <v>7</v>
       </c>
-      <c r="L13">
+      <c r="O13">
         <v>6</v>
       </c>
-      <c r="M13">
+      <c r="P13">
         <v>50</v>
       </c>
-      <c r="N13">
-        <v>2</v>
-      </c>
-      <c r="O13">
-        <v>4</v>
-      </c>
-      <c r="P13">
-        <v>3</v>
-      </c>
       <c r="Q13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R13">
+        <v>4</v>
+      </c>
+      <c r="S13">
+        <v>3</v>
+      </c>
+      <c r="T13">
+        <v>4</v>
+      </c>
+      <c r="U13">
         <v>44</v>
       </c>
-      <c r="S13">
+      <c r="V13">
         <v>40</v>
       </c>
-      <c r="T13">
-        <v>2</v>
-      </c>
-      <c r="U13">
-        <v>2</v>
-      </c>
-      <c r="V13">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13">
+        <v>2</v>
+      </c>
+      <c r="X13">
+        <v>2</v>
+      </c>
+      <c r="Y13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -1432,54 +1560,63 @@
         <v>5</v>
       </c>
       <c r="F14">
+        <v>4</v>
+      </c>
+      <c r="G14">
+        <v>3</v>
+      </c>
+      <c r="H14">
+        <v>2</v>
+      </c>
+      <c r="I14">
         <v>0.8567524752138409</v>
       </c>
-      <c r="G14">
+      <c r="J14">
         <v>58</v>
       </c>
-      <c r="H14">
+      <c r="K14">
         <v>9.6551724137930997</v>
       </c>
-      <c r="I14">
+      <c r="L14">
         <v>1</v>
       </c>
-      <c r="J14">
+      <c r="M14">
         <v>24</v>
       </c>
-      <c r="K14">
+      <c r="N14">
         <v>42</v>
       </c>
-      <c r="L14">
-        <v>4</v>
-      </c>
-      <c r="M14">
+      <c r="O14">
+        <v>4</v>
+      </c>
+      <c r="P14">
         <v>50</v>
       </c>
-      <c r="N14">
-        <v>2</v>
-      </c>
-      <c r="O14">
+      <c r="Q14">
+        <v>2</v>
+      </c>
+      <c r="R14">
         <v>5</v>
       </c>
-      <c r="P14">
-        <v>3</v>
-      </c>
-      <c r="Q14">
-        <v>3</v>
-      </c>
-      <c r="R14">
+      <c r="S14">
+        <v>3</v>
+      </c>
+      <c r="T14">
+        <v>3</v>
+      </c>
+      <c r="U14">
         <v>16</v>
       </c>
-      <c r="S14">
+      <c r="V14">
         <v>16</v>
       </c>
-      <c r="T14">
-        <v>2</v>
-      </c>
-      <c r="U14">
-        <v>2</v>
-      </c>
-      <c r="V14">
+      <c r="W14">
+        <v>2</v>
+      </c>
+      <c r="X14">
+        <v>2</v>
+      </c>
+      <c r="Y14">
         <v>3</v>
       </c>
     </row>

--- a/r_test/plot_metrics/Plot_Metrics_Combined.xlsx
+++ b/r_test/plot_metrics/Plot_Metrics_Combined.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10720"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/patrickangst/Documents/GitHub/UWW200_Master_Thesis_public/r_test/plot_metrics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8D0FCD6-7371-B241-BF72-AC844E9D03D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD5D7F1C-9784-C640-9B29-2FC1B344379F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57680" yWindow="500" windowWidth="18980" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1860" windowWidth="34560" windowHeight="20100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="44">
   <si>
     <t>Testsite</t>
   </si>
@@ -162,6 +162,12 @@
   </si>
   <si>
     <t>Unique_Habitat_Types_Short3</t>
+  </si>
+  <si>
+    <t>Unique_Spectral_Species_WCSS_Custom</t>
+  </si>
+  <si>
+    <t>Unique_Spectral_Species_WCSS_Custom_Unmasked</t>
   </si>
 </sst>
 </file>
@@ -514,7 +520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y14"/>
+  <dimension ref="A1:AA14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.83203125" bestFit="1" customWidth="1"/>
@@ -529,20 +535,22 @@
     <col min="11" max="12" width="15.83203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="28.1640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="31.83203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="25.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="29.83203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="26.33203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="30.83203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="31.1640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="27.83203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="34" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="42.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="31.83203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="29.83203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="29" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="30.83203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="31.1640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="27.83203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -586,40 +594,46 @@
         <v>33</v>
       </c>
       <c r="O1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -663,40 +677,46 @@
         <v>26</v>
       </c>
       <c r="O2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P2">
+        <v>8</v>
+      </c>
+      <c r="Q2">
+        <v>4</v>
+      </c>
+      <c r="R2">
         <v>46</v>
       </c>
-      <c r="Q2">
-        <v>2</v>
-      </c>
-      <c r="R2">
-        <v>4</v>
-      </c>
       <c r="S2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U2">
+        <v>3</v>
+      </c>
+      <c r="V2">
+        <v>3</v>
+      </c>
+      <c r="W2">
         <v>39</v>
       </c>
-      <c r="V2">
+      <c r="X2">
         <v>39</v>
       </c>
-      <c r="W2">
-        <v>3</v>
-      </c>
-      <c r="X2">
-        <v>2</v>
-      </c>
       <c r="Y2">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z2">
+        <v>2</v>
+      </c>
+      <c r="AA2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -740,40 +760,46 @@
         <v>12</v>
       </c>
       <c r="O3">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="P3">
+        <v>5</v>
+      </c>
+      <c r="Q3">
+        <v>4</v>
+      </c>
+      <c r="R3">
         <v>45</v>
       </c>
-      <c r="Q3">
-        <v>4</v>
-      </c>
-      <c r="R3">
+      <c r="S3">
+        <v>4</v>
+      </c>
+      <c r="T3">
         <v>6</v>
       </c>
-      <c r="S3">
-        <v>3</v>
-      </c>
-      <c r="T3">
-        <v>3</v>
-      </c>
       <c r="U3">
+        <v>3</v>
+      </c>
+      <c r="V3">
+        <v>3</v>
+      </c>
+      <c r="W3">
         <v>8</v>
       </c>
-      <c r="V3">
+      <c r="X3">
         <v>6</v>
       </c>
-      <c r="W3">
-        <v>3</v>
-      </c>
-      <c r="X3">
-        <v>3</v>
-      </c>
       <c r="Y3">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z3">
+        <v>3</v>
+      </c>
+      <c r="AA3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -817,40 +843,46 @@
         <v>43</v>
       </c>
       <c r="O4">
+        <v>11</v>
+      </c>
+      <c r="P4">
+        <v>26</v>
+      </c>
+      <c r="Q4">
         <v>6</v>
       </c>
-      <c r="P4">
+      <c r="R4">
         <v>50</v>
       </c>
-      <c r="Q4">
-        <v>2</v>
-      </c>
-      <c r="R4">
-        <v>4</v>
-      </c>
       <c r="S4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U4">
+        <v>3</v>
+      </c>
+      <c r="V4">
+        <v>3</v>
+      </c>
+      <c r="W4">
         <v>38</v>
       </c>
-      <c r="V4">
+      <c r="X4">
         <v>35</v>
       </c>
-      <c r="W4">
-        <v>2</v>
-      </c>
-      <c r="X4">
-        <v>2</v>
-      </c>
       <c r="Y4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="Z4">
+        <v>2</v>
+      </c>
+      <c r="AA4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -894,40 +926,46 @@
         <v>40</v>
       </c>
       <c r="O5">
+        <v>19</v>
+      </c>
+      <c r="P5">
+        <v>4</v>
+      </c>
+      <c r="Q5">
         <v>5</v>
       </c>
-      <c r="P5">
+      <c r="R5">
         <v>50</v>
       </c>
-      <c r="Q5">
-        <v>2</v>
-      </c>
-      <c r="R5">
+      <c r="S5">
+        <v>2</v>
+      </c>
+      <c r="T5">
         <v>5</v>
       </c>
-      <c r="S5">
-        <v>3</v>
-      </c>
-      <c r="T5">
-        <v>3</v>
-      </c>
       <c r="U5">
+        <v>3</v>
+      </c>
+      <c r="V5">
+        <v>3</v>
+      </c>
+      <c r="W5">
         <v>20</v>
       </c>
-      <c r="V5">
+      <c r="X5">
         <v>17</v>
       </c>
-      <c r="W5">
-        <v>2</v>
-      </c>
-      <c r="X5">
-        <v>2</v>
-      </c>
       <c r="Y5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="Z5">
+        <v>2</v>
+      </c>
+      <c r="AA5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -971,40 +1009,46 @@
         <v>25</v>
       </c>
       <c r="O6">
+        <v>37</v>
+      </c>
+      <c r="P6">
+        <v>7</v>
+      </c>
+      <c r="Q6">
         <v>6</v>
       </c>
-      <c r="P6">
+      <c r="R6">
         <v>48</v>
       </c>
-      <c r="Q6">
-        <v>2</v>
-      </c>
-      <c r="R6">
-        <v>3</v>
-      </c>
       <c r="S6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T6">
         <v>3</v>
       </c>
       <c r="U6">
+        <v>3</v>
+      </c>
+      <c r="V6">
+        <v>3</v>
+      </c>
+      <c r="W6">
         <v>5</v>
       </c>
-      <c r="V6">
-        <v>3</v>
-      </c>
-      <c r="W6">
-        <v>3</v>
-      </c>
       <c r="X6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y6">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z6">
+        <v>2</v>
+      </c>
+      <c r="AA6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1048,40 +1092,46 @@
         <v>27</v>
       </c>
       <c r="O7">
+        <v>9</v>
+      </c>
+      <c r="P7">
+        <v>13</v>
+      </c>
+      <c r="Q7">
         <v>5</v>
       </c>
-      <c r="P7">
+      <c r="R7">
         <v>50</v>
       </c>
-      <c r="Q7">
-        <v>2</v>
-      </c>
-      <c r="R7">
+      <c r="S7">
+        <v>2</v>
+      </c>
+      <c r="T7">
         <v>8</v>
       </c>
-      <c r="S7">
-        <v>3</v>
-      </c>
-      <c r="T7">
-        <v>3</v>
-      </c>
       <c r="U7">
+        <v>3</v>
+      </c>
+      <c r="V7">
+        <v>3</v>
+      </c>
+      <c r="W7">
         <v>15</v>
       </c>
-      <c r="V7">
+      <c r="X7">
         <v>32</v>
       </c>
-      <c r="W7">
-        <v>2</v>
-      </c>
-      <c r="X7">
-        <v>2</v>
-      </c>
       <c r="Y7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="Z7">
+        <v>2</v>
+      </c>
+      <c r="AA7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1125,40 +1175,46 @@
         <v>11</v>
       </c>
       <c r="O8">
+        <v>44</v>
+      </c>
+      <c r="P8">
+        <v>13</v>
+      </c>
+      <c r="Q8">
         <v>6</v>
       </c>
-      <c r="P8">
+      <c r="R8">
         <v>48</v>
       </c>
-      <c r="Q8">
-        <v>2</v>
-      </c>
-      <c r="R8">
-        <v>3</v>
-      </c>
       <c r="S8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T8">
         <v>3</v>
       </c>
       <c r="U8">
+        <v>3</v>
+      </c>
+      <c r="V8">
+        <v>3</v>
+      </c>
+      <c r="W8">
         <v>5</v>
       </c>
-      <c r="V8">
+      <c r="X8">
         <v>48</v>
       </c>
-      <c r="W8">
-        <v>3</v>
-      </c>
-      <c r="X8">
-        <v>2</v>
-      </c>
       <c r="Y8">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8">
+        <v>2</v>
+      </c>
+      <c r="AA8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -1202,40 +1258,46 @@
         <v>27</v>
       </c>
       <c r="O9">
+        <v>5</v>
+      </c>
+      <c r="P9">
+        <v>5</v>
+      </c>
+      <c r="Q9">
         <v>12</v>
       </c>
-      <c r="P9">
+      <c r="R9">
         <v>50</v>
       </c>
-      <c r="Q9">
-        <v>2</v>
-      </c>
-      <c r="R9">
+      <c r="S9">
+        <v>2</v>
+      </c>
+      <c r="T9">
         <v>8</v>
       </c>
-      <c r="S9">
-        <v>3</v>
-      </c>
-      <c r="T9">
-        <v>3</v>
-      </c>
       <c r="U9">
+        <v>3</v>
+      </c>
+      <c r="V9">
+        <v>3</v>
+      </c>
+      <c r="W9">
         <v>42</v>
       </c>
-      <c r="V9">
+      <c r="X9">
         <v>14</v>
       </c>
-      <c r="W9">
-        <v>2</v>
-      </c>
-      <c r="X9">
-        <v>2</v>
-      </c>
       <c r="Y9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="Z9">
+        <v>2</v>
+      </c>
+      <c r="AA9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1279,40 +1341,46 @@
         <v>7</v>
       </c>
       <c r="O10">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="P10">
+        <v>36</v>
+      </c>
+      <c r="Q10">
+        <v>3</v>
+      </c>
+      <c r="R10">
         <v>50</v>
       </c>
-      <c r="Q10">
+      <c r="S10">
         <v>20</v>
       </c>
-      <c r="R10">
+      <c r="T10">
         <v>9</v>
       </c>
-      <c r="S10">
-        <v>3</v>
-      </c>
-      <c r="T10">
-        <v>3</v>
-      </c>
       <c r="U10">
+        <v>3</v>
+      </c>
+      <c r="V10">
+        <v>3</v>
+      </c>
+      <c r="W10">
         <v>39</v>
       </c>
-      <c r="V10">
+      <c r="X10">
         <v>40</v>
       </c>
-      <c r="W10">
-        <v>2</v>
-      </c>
-      <c r="X10">
-        <v>2</v>
-      </c>
       <c r="Y10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="Z10">
+        <v>2</v>
+      </c>
+      <c r="AA10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -1356,40 +1424,46 @@
         <v>48</v>
       </c>
       <c r="O11">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="P11">
+        <v>20</v>
+      </c>
+      <c r="Q11">
+        <v>4</v>
+      </c>
+      <c r="R11">
         <v>50</v>
       </c>
-      <c r="Q11">
-        <v>3</v>
-      </c>
-      <c r="R11">
+      <c r="S11">
+        <v>3</v>
+      </c>
+      <c r="T11">
         <v>10</v>
       </c>
-      <c r="S11">
-        <v>3</v>
-      </c>
-      <c r="T11">
-        <v>3</v>
-      </c>
       <c r="U11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V11">
+        <v>3</v>
+      </c>
+      <c r="W11">
+        <v>4</v>
+      </c>
+      <c r="X11">
         <v>41</v>
       </c>
-      <c r="W11">
-        <v>3</v>
-      </c>
-      <c r="X11">
-        <v>2</v>
-      </c>
       <c r="Y11">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11">
+        <v>2</v>
+      </c>
+      <c r="AA11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -1433,40 +1507,46 @@
         <v>5</v>
       </c>
       <c r="O12">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="P12">
+        <v>18</v>
+      </c>
+      <c r="Q12">
+        <v>3</v>
+      </c>
+      <c r="R12">
         <v>50</v>
       </c>
-      <c r="Q12">
-        <v>2</v>
-      </c>
-      <c r="R12">
+      <c r="S12">
+        <v>2</v>
+      </c>
+      <c r="T12">
         <v>8</v>
       </c>
-      <c r="S12">
-        <v>3</v>
-      </c>
-      <c r="T12">
-        <v>3</v>
-      </c>
       <c r="U12">
+        <v>3</v>
+      </c>
+      <c r="V12">
+        <v>3</v>
+      </c>
+      <c r="W12">
         <v>42</v>
       </c>
-      <c r="V12">
+      <c r="X12">
         <v>37</v>
       </c>
-      <c r="W12">
-        <v>3</v>
-      </c>
-      <c r="X12">
-        <v>3</v>
-      </c>
       <c r="Y12">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12">
+        <v>3</v>
+      </c>
+      <c r="AA12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -1510,40 +1590,46 @@
         <v>7</v>
       </c>
       <c r="O13">
+        <v>26</v>
+      </c>
+      <c r="P13">
+        <v>12</v>
+      </c>
+      <c r="Q13">
         <v>6</v>
       </c>
-      <c r="P13">
+      <c r="R13">
         <v>50</v>
       </c>
-      <c r="Q13">
-        <v>2</v>
-      </c>
-      <c r="R13">
-        <v>4</v>
-      </c>
       <c r="S13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T13">
         <v>4</v>
       </c>
       <c r="U13">
+        <v>3</v>
+      </c>
+      <c r="V13">
+        <v>4</v>
+      </c>
+      <c r="W13">
         <v>44</v>
       </c>
-      <c r="V13">
+      <c r="X13">
         <v>40</v>
       </c>
-      <c r="W13">
-        <v>2</v>
-      </c>
-      <c r="X13">
-        <v>2</v>
-      </c>
       <c r="Y13">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="Z13">
+        <v>2</v>
+      </c>
+      <c r="AA13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -1587,36 +1673,42 @@
         <v>42</v>
       </c>
       <c r="O14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P14">
+        <v>6</v>
+      </c>
+      <c r="Q14">
+        <v>4</v>
+      </c>
+      <c r="R14">
         <v>50</v>
       </c>
-      <c r="Q14">
-        <v>2</v>
-      </c>
-      <c r="R14">
+      <c r="S14">
+        <v>2</v>
+      </c>
+      <c r="T14">
         <v>5</v>
       </c>
-      <c r="S14">
-        <v>3</v>
-      </c>
-      <c r="T14">
-        <v>3</v>
-      </c>
       <c r="U14">
+        <v>3</v>
+      </c>
+      <c r="V14">
+        <v>3</v>
+      </c>
+      <c r="W14">
         <v>16</v>
       </c>
-      <c r="V14">
+      <c r="X14">
         <v>16</v>
       </c>
-      <c r="W14">
-        <v>2</v>
-      </c>
-      <c r="X14">
-        <v>2</v>
-      </c>
       <c r="Y14">
+        <v>2</v>
+      </c>
+      <c r="Z14">
+        <v>2</v>
+      </c>
+      <c r="AA14">
         <v>3</v>
       </c>
     </row>
@@ -1627,18 +1719,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4CB34EE-4F67-4477-8FF9-41D97ADB11AC}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.1640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="27.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1654,8 +1747,11 @@
       <c r="E1" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F1" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1671,8 +1767,11 @@
       <c r="E2">
         <v>43</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1688,8 +1787,11 @@
       <c r="E3">
         <v>40</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1705,8 +1807,11 @@
       <c r="E4">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F4">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1722,8 +1827,11 @@
       <c r="E5">
         <v>27</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1739,8 +1847,11 @@
       <c r="E6">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F6">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1756,8 +1867,11 @@
       <c r="E7">
         <v>27</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -1773,8 +1887,11 @@
       <c r="E8">
         <v>48</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1790,8 +1907,11 @@
       <c r="E9">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F9">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -1807,8 +1927,11 @@
       <c r="E10">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F10">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -1823,6 +1946,9 @@
       </c>
       <c r="E11">
         <v>42</v>
+      </c>
+      <c r="F11">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1832,17 +1958,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1939FA77-8242-4C4C-B69D-486772391B8B}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1858,8 +1985,11 @@
       <c r="E1" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F1" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1875,8 +2005,11 @@
       <c r="E2">
         <v>26</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1892,8 +2025,11 @@
       <c r="E3">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1908,6 +2044,9 @@
       </c>
       <c r="E4">
         <v>7</v>
+      </c>
+      <c r="F4">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/r_test/plot_metrics/Plot_Metrics_Combined.xlsx
+++ b/r_test/plot_metrics/Plot_Metrics_Combined.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/patrickangst/Documents/GitHub/UWW200_Master_Thesis_public/r_test/plot_metrics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD5D7F1C-9784-C640-9B29-2FC1B344379F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68301C40-8AA5-9E47-A5F1-89242CE0B930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1860" windowWidth="34560" windowHeight="20100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20580" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="part_c_d" sheetId="3" r:id="rId2"/>
     <sheet name="part_e" sheetId="4" r:id="rId3"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId4"/>
+    <sheet name="NbClust" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="57">
   <si>
     <t>Testsite</t>
   </si>
@@ -168,13 +169,52 @@
   </si>
   <si>
     <t>Unique_Spectral_Species_WCSS_Custom_Unmasked</t>
+  </si>
+  <si>
+    <t>Unique_Spectral_Species_WCSS_Custom_Normalized</t>
+  </si>
+  <si>
+    <t>ratkowsky</t>
+  </si>
+  <si>
+    <t>sdbw</t>
+  </si>
+  <si>
+    <t>db</t>
+  </si>
+  <si>
+    <t>sdindex</t>
+  </si>
+  <si>
+    <t>ball</t>
+  </si>
+  <si>
+    <t>tracew</t>
+  </si>
+  <si>
+    <t>friedman</t>
+  </si>
+  <si>
+    <t>rubin</t>
+  </si>
+  <si>
+    <t>pseudot2</t>
+  </si>
+  <si>
+    <t>beale</t>
+  </si>
+  <si>
+    <t>trcovw</t>
+  </si>
+  <si>
+    <t>Test site</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -186,6 +226,21 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -211,11 +266,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -520,7 +579,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA14"/>
+  <dimension ref="A1:AB14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.83203125" bestFit="1" customWidth="1"/>
@@ -536,21 +595,22 @@
     <col min="13" max="13" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="28.1640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="34" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="42.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="31.83203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="25.33203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="29.83203125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="26.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="29" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="30.83203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="31.1640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="27.83203125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="29" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="43.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="42.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="31.83203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="29.83203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="30.83203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="31.1640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="27.83203125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -597,43 +657,46 @@
         <v>42</v>
       </c>
       <c r="P1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -680,43 +743,46 @@
         <v>7</v>
       </c>
       <c r="P2">
+        <v>35</v>
+      </c>
+      <c r="Q2">
         <v>8</v>
       </c>
-      <c r="Q2">
-        <v>4</v>
-      </c>
       <c r="R2">
+        <v>4</v>
+      </c>
+      <c r="S2">
         <v>46</v>
       </c>
-      <c r="S2">
-        <v>2</v>
-      </c>
       <c r="T2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V2">
         <v>3</v>
       </c>
       <c r="W2">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="X2">
         <v>39</v>
       </c>
       <c r="Y2">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="Z2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="AB2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -760,46 +826,49 @@
         <v>12</v>
       </c>
       <c r="O3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P3">
+        <v>13</v>
+      </c>
+      <c r="Q3">
         <v>5</v>
       </c>
-      <c r="Q3">
-        <v>4</v>
-      </c>
       <c r="R3">
+        <v>4</v>
+      </c>
+      <c r="S3">
         <v>45</v>
       </c>
-      <c r="S3">
-        <v>4</v>
-      </c>
       <c r="T3">
+        <v>4</v>
+      </c>
+      <c r="U3">
         <v>6</v>
       </c>
-      <c r="U3">
-        <v>3</v>
-      </c>
       <c r="V3">
         <v>3</v>
       </c>
       <c r="W3">
+        <v>3</v>
+      </c>
+      <c r="X3">
         <v>8</v>
       </c>
-      <c r="X3">
+      <c r="Y3">
         <v>6</v>
       </c>
-      <c r="Y3">
-        <v>3</v>
-      </c>
       <c r="Z3">
         <v>3</v>
       </c>
       <c r="AA3">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -843,46 +912,49 @@
         <v>43</v>
       </c>
       <c r="O4">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="P4">
+        <v>45</v>
+      </c>
+      <c r="Q4">
         <v>26</v>
       </c>
-      <c r="Q4">
+      <c r="R4">
         <v>6</v>
       </c>
-      <c r="R4">
+      <c r="S4">
         <v>50</v>
       </c>
-      <c r="S4">
-        <v>2</v>
-      </c>
       <c r="T4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V4">
         <v>3</v>
       </c>
       <c r="W4">
+        <v>3</v>
+      </c>
+      <c r="X4">
         <v>38</v>
       </c>
-      <c r="X4">
+      <c r="Y4">
         <v>35</v>
       </c>
-      <c r="Y4">
-        <v>2</v>
-      </c>
       <c r="Z4">
         <v>2</v>
       </c>
       <c r="AA4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="AB4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -926,46 +998,49 @@
         <v>40</v>
       </c>
       <c r="O5">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="P5">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="Q5">
+        <v>4</v>
+      </c>
+      <c r="R5">
         <v>5</v>
       </c>
-      <c r="R5">
+      <c r="S5">
         <v>50</v>
       </c>
-      <c r="S5">
-        <v>2</v>
-      </c>
       <c r="T5">
+        <v>2</v>
+      </c>
+      <c r="U5">
         <v>5</v>
       </c>
-      <c r="U5">
-        <v>3</v>
-      </c>
       <c r="V5">
         <v>3</v>
       </c>
       <c r="W5">
+        <v>3</v>
+      </c>
+      <c r="X5">
         <v>20</v>
       </c>
-      <c r="X5">
+      <c r="Y5">
         <v>17</v>
       </c>
-      <c r="Y5">
-        <v>2</v>
-      </c>
       <c r="Z5">
         <v>2</v>
       </c>
       <c r="AA5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="AB5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1009,22 +1084,22 @@
         <v>25</v>
       </c>
       <c r="O6">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="P6">
+        <v>24</v>
+      </c>
+      <c r="Q6">
         <v>7</v>
       </c>
-      <c r="Q6">
+      <c r="R6">
         <v>6</v>
       </c>
-      <c r="R6">
+      <c r="S6">
         <v>48</v>
       </c>
-      <c r="S6">
-        <v>2</v>
-      </c>
       <c r="T6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U6">
         <v>3</v>
@@ -1033,22 +1108,25 @@
         <v>3</v>
       </c>
       <c r="W6">
+        <v>3</v>
+      </c>
+      <c r="X6">
         <v>5</v>
       </c>
-      <c r="X6">
-        <v>3</v>
-      </c>
       <c r="Y6">
         <v>3</v>
       </c>
       <c r="Z6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="AB6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1092,46 +1170,49 @@
         <v>27</v>
       </c>
       <c r="O7">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="P7">
         <v>13</v>
       </c>
       <c r="Q7">
+        <v>13</v>
+      </c>
+      <c r="R7">
         <v>5</v>
       </c>
-      <c r="R7">
+      <c r="S7">
         <v>50</v>
       </c>
-      <c r="S7">
-        <v>2</v>
-      </c>
       <c r="T7">
+        <v>2</v>
+      </c>
+      <c r="U7">
         <v>8</v>
       </c>
-      <c r="U7">
-        <v>3</v>
-      </c>
       <c r="V7">
         <v>3</v>
       </c>
       <c r="W7">
+        <v>3</v>
+      </c>
+      <c r="X7">
         <v>15</v>
       </c>
-      <c r="X7">
+      <c r="Y7">
         <v>32</v>
       </c>
-      <c r="Y7">
-        <v>2</v>
-      </c>
       <c r="Z7">
         <v>2</v>
       </c>
       <c r="AA7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="AB7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1175,22 +1256,22 @@
         <v>11</v>
       </c>
       <c r="O8">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P8">
+        <v>9</v>
+      </c>
+      <c r="Q8">
         <v>13</v>
       </c>
-      <c r="Q8">
+      <c r="R8">
         <v>6</v>
       </c>
-      <c r="R8">
+      <c r="S8">
         <v>48</v>
       </c>
-      <c r="S8">
-        <v>2</v>
-      </c>
       <c r="T8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U8">
         <v>3</v>
@@ -1199,22 +1280,25 @@
         <v>3</v>
       </c>
       <c r="W8">
+        <v>3</v>
+      </c>
+      <c r="X8">
         <v>5</v>
       </c>
-      <c r="X8">
+      <c r="Y8">
         <v>48</v>
       </c>
-      <c r="Y8">
-        <v>3</v>
-      </c>
       <c r="Z8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="AB8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -1258,46 +1342,49 @@
         <v>27</v>
       </c>
       <c r="O9">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="P9">
         <v>5</v>
       </c>
       <c r="Q9">
+        <v>5</v>
+      </c>
+      <c r="R9">
         <v>12</v>
       </c>
-      <c r="R9">
+      <c r="S9">
         <v>50</v>
       </c>
-      <c r="S9">
-        <v>2</v>
-      </c>
       <c r="T9">
+        <v>2</v>
+      </c>
+      <c r="U9">
         <v>8</v>
       </c>
-      <c r="U9">
-        <v>3</v>
-      </c>
       <c r="V9">
         <v>3</v>
       </c>
       <c r="W9">
+        <v>3</v>
+      </c>
+      <c r="X9">
         <v>42</v>
       </c>
-      <c r="X9">
+      <c r="Y9">
         <v>14</v>
       </c>
-      <c r="Y9">
-        <v>2</v>
-      </c>
       <c r="Z9">
         <v>2</v>
       </c>
       <c r="AA9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="AB9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1341,46 +1428,49 @@
         <v>7</v>
       </c>
       <c r="O10">
+        <v>40</v>
+      </c>
+      <c r="P10">
+        <v>34</v>
+      </c>
+      <c r="Q10">
         <v>36</v>
       </c>
-      <c r="P10">
-        <v>36</v>
-      </c>
-      <c r="Q10">
-        <v>3</v>
-      </c>
       <c r="R10">
+        <v>3</v>
+      </c>
+      <c r="S10">
         <v>50</v>
       </c>
-      <c r="S10">
+      <c r="T10">
         <v>20</v>
       </c>
-      <c r="T10">
+      <c r="U10">
         <v>9</v>
       </c>
-      <c r="U10">
-        <v>3</v>
-      </c>
       <c r="V10">
         <v>3</v>
       </c>
       <c r="W10">
+        <v>3</v>
+      </c>
+      <c r="X10">
         <v>39</v>
       </c>
-      <c r="X10">
+      <c r="Y10">
         <v>40</v>
       </c>
-      <c r="Y10">
-        <v>2</v>
-      </c>
       <c r="Z10">
         <v>2</v>
       </c>
       <c r="AA10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="AB10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -1424,46 +1514,49 @@
         <v>48</v>
       </c>
       <c r="O11">
+        <v>48</v>
+      </c>
+      <c r="P11">
+        <v>21</v>
+      </c>
+      <c r="Q11">
+        <v>20</v>
+      </c>
+      <c r="R11">
+        <v>4</v>
+      </c>
+      <c r="S11">
+        <v>50</v>
+      </c>
+      <c r="T11">
+        <v>3</v>
+      </c>
+      <c r="U11">
         <v>10</v>
       </c>
-      <c r="P11">
-        <v>20</v>
-      </c>
-      <c r="Q11">
-        <v>4</v>
-      </c>
-      <c r="R11">
-        <v>50</v>
-      </c>
-      <c r="S11">
-        <v>3</v>
-      </c>
-      <c r="T11">
-        <v>10</v>
-      </c>
-      <c r="U11">
-        <v>3</v>
-      </c>
       <c r="V11">
         <v>3</v>
       </c>
       <c r="W11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X11">
+        <v>4</v>
+      </c>
+      <c r="Y11">
         <v>41</v>
       </c>
-      <c r="Y11">
-        <v>3</v>
-      </c>
       <c r="Z11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="AB11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -1507,46 +1600,49 @@
         <v>5</v>
       </c>
       <c r="O12">
+        <v>23</v>
+      </c>
+      <c r="P12">
+        <v>13</v>
+      </c>
+      <c r="Q12">
         <v>18</v>
       </c>
-      <c r="P12">
-        <v>18</v>
-      </c>
-      <c r="Q12">
-        <v>3</v>
-      </c>
       <c r="R12">
+        <v>3</v>
+      </c>
+      <c r="S12">
         <v>50</v>
       </c>
-      <c r="S12">
-        <v>2</v>
-      </c>
       <c r="T12">
+        <v>2</v>
+      </c>
+      <c r="U12">
         <v>8</v>
       </c>
-      <c r="U12">
-        <v>3</v>
-      </c>
       <c r="V12">
         <v>3</v>
       </c>
       <c r="W12">
+        <v>3</v>
+      </c>
+      <c r="X12">
         <v>42</v>
       </c>
-      <c r="X12">
+      <c r="Y12">
         <v>37</v>
       </c>
-      <c r="Y12">
-        <v>3</v>
-      </c>
       <c r="Z12">
         <v>3</v>
       </c>
       <c r="AA12">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -1590,46 +1686,49 @@
         <v>7</v>
       </c>
       <c r="O13">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="P13">
+        <v>24</v>
+      </c>
+      <c r="Q13">
         <v>12</v>
       </c>
-      <c r="Q13">
+      <c r="R13">
         <v>6</v>
       </c>
-      <c r="R13">
+      <c r="S13">
         <v>50</v>
       </c>
-      <c r="S13">
-        <v>2</v>
-      </c>
       <c r="T13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W13">
+        <v>4</v>
+      </c>
+      <c r="X13">
         <v>44</v>
       </c>
-      <c r="X13">
+      <c r="Y13">
         <v>40</v>
       </c>
-      <c r="Y13">
-        <v>2</v>
-      </c>
       <c r="Z13">
         <v>2</v>
       </c>
       <c r="AA13">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="AB13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -1673,42 +1772,45 @@
         <v>42</v>
       </c>
       <c r="O14">
+        <v>48</v>
+      </c>
+      <c r="P14">
+        <v>10</v>
+      </c>
+      <c r="Q14">
+        <v>6</v>
+      </c>
+      <c r="R14">
+        <v>4</v>
+      </c>
+      <c r="S14">
+        <v>50</v>
+      </c>
+      <c r="T14">
+        <v>2</v>
+      </c>
+      <c r="U14">
         <v>5</v>
       </c>
-      <c r="P14">
-        <v>6</v>
-      </c>
-      <c r="Q14">
-        <v>4</v>
-      </c>
-      <c r="R14">
-        <v>50</v>
-      </c>
-      <c r="S14">
-        <v>2</v>
-      </c>
-      <c r="T14">
-        <v>5</v>
-      </c>
-      <c r="U14">
-        <v>3</v>
-      </c>
       <c r="V14">
         <v>3</v>
       </c>
       <c r="W14">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="X14">
         <v>16</v>
       </c>
       <c r="Y14">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="Z14">
         <v>2</v>
       </c>
       <c r="AA14">
+        <v>2</v>
+      </c>
+      <c r="AB14">
         <v>3</v>
       </c>
     </row>
@@ -1719,7 +1821,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4CB34EE-4F67-4477-8FF9-41D97ADB11AC}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
@@ -1728,10 +1830,10 @@
     <col min="4" max="4" width="18.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="33.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1750,8 +1852,11 @@
       <c r="F1" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G1" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1770,8 +1875,11 @@
       <c r="F2">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1790,8 +1898,11 @@
       <c r="F3">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1810,8 +1921,11 @@
       <c r="F4">
         <v>37</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1830,8 +1944,11 @@
       <c r="F5">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1850,8 +1967,11 @@
       <c r="F6">
         <v>44</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1870,8 +1990,11 @@
       <c r="F7">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -1890,8 +2013,11 @@
       <c r="F8">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G8">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1910,8 +2036,11 @@
       <c r="F9">
         <v>18</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -1930,8 +2059,11 @@
       <c r="F10">
         <v>26</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G10">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -1949,6 +2081,9 @@
       </c>
       <c r="F11">
         <v>5</v>
+      </c>
+      <c r="G11">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1958,7 +2093,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1939FA77-8242-4C4C-B69D-486772391B8B}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
@@ -1967,9 +2102,10 @@
     <col min="4" max="4" width="18.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="33.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1988,8 +2124,11 @@
       <c r="F1" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G1" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -2008,8 +2147,11 @@
       <c r="F2">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -2028,8 +2170,11 @@
       <c r="F3">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -2047,6 +2192,9 @@
       </c>
       <c r="F4">
         <v>36</v>
+      </c>
+      <c r="G4">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -2308,4 +2456,559 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FD9D7EF-CDCD-DA4C-A506-BEB45A8AA3CD}">
+  <dimension ref="A1:L14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="27.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3">
+        <v>46</v>
+      </c>
+      <c r="D2" s="3">
+        <v>2</v>
+      </c>
+      <c r="E2" s="3">
+        <v>4</v>
+      </c>
+      <c r="F2" s="3">
+        <v>3</v>
+      </c>
+      <c r="G2" s="3">
+        <v>3</v>
+      </c>
+      <c r="H2" s="3">
+        <v>39</v>
+      </c>
+      <c r="I2" s="3">
+        <v>39</v>
+      </c>
+      <c r="J2" s="3">
+        <v>3</v>
+      </c>
+      <c r="K2" s="3">
+        <v>2</v>
+      </c>
+      <c r="L2" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3">
+        <v>45</v>
+      </c>
+      <c r="D3" s="3">
+        <v>4</v>
+      </c>
+      <c r="E3" s="3">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3">
+        <v>3</v>
+      </c>
+      <c r="G3" s="3">
+        <v>3</v>
+      </c>
+      <c r="H3" s="3">
+        <v>8</v>
+      </c>
+      <c r="I3" s="3">
+        <v>6</v>
+      </c>
+      <c r="J3" s="3">
+        <v>3</v>
+      </c>
+      <c r="K3" s="3">
+        <v>3</v>
+      </c>
+      <c r="L3" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="3">
+        <v>6</v>
+      </c>
+      <c r="C4" s="3">
+        <v>50</v>
+      </c>
+      <c r="D4" s="3">
+        <v>2</v>
+      </c>
+      <c r="E4" s="3">
+        <v>4</v>
+      </c>
+      <c r="F4" s="3">
+        <v>3</v>
+      </c>
+      <c r="G4" s="3">
+        <v>3</v>
+      </c>
+      <c r="H4" s="3">
+        <v>38</v>
+      </c>
+      <c r="I4" s="3">
+        <v>35</v>
+      </c>
+      <c r="J4" s="3">
+        <v>2</v>
+      </c>
+      <c r="K4" s="3">
+        <v>2</v>
+      </c>
+      <c r="L4" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="3">
+        <v>5</v>
+      </c>
+      <c r="C5" s="3">
+        <v>50</v>
+      </c>
+      <c r="D5" s="3">
+        <v>2</v>
+      </c>
+      <c r="E5" s="3">
+        <v>5</v>
+      </c>
+      <c r="F5" s="3">
+        <v>3</v>
+      </c>
+      <c r="G5" s="3">
+        <v>3</v>
+      </c>
+      <c r="H5" s="3">
+        <v>20</v>
+      </c>
+      <c r="I5" s="3">
+        <v>17</v>
+      </c>
+      <c r="J5" s="3">
+        <v>2</v>
+      </c>
+      <c r="K5" s="3">
+        <v>2</v>
+      </c>
+      <c r="L5" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="3">
+        <v>6</v>
+      </c>
+      <c r="C6" s="3">
+        <v>48</v>
+      </c>
+      <c r="D6" s="3">
+        <v>2</v>
+      </c>
+      <c r="E6" s="3">
+        <v>3</v>
+      </c>
+      <c r="F6" s="3">
+        <v>3</v>
+      </c>
+      <c r="G6" s="3">
+        <v>3</v>
+      </c>
+      <c r="H6" s="3">
+        <v>5</v>
+      </c>
+      <c r="I6" s="3">
+        <v>3</v>
+      </c>
+      <c r="J6" s="3">
+        <v>3</v>
+      </c>
+      <c r="K6" s="3">
+        <v>2</v>
+      </c>
+      <c r="L6" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="3">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3">
+        <v>50</v>
+      </c>
+      <c r="D7" s="3">
+        <v>2</v>
+      </c>
+      <c r="E7" s="3">
+        <v>8</v>
+      </c>
+      <c r="F7" s="3">
+        <v>3</v>
+      </c>
+      <c r="G7" s="3">
+        <v>3</v>
+      </c>
+      <c r="H7" s="3">
+        <v>15</v>
+      </c>
+      <c r="I7" s="3">
+        <v>32</v>
+      </c>
+      <c r="J7" s="3">
+        <v>2</v>
+      </c>
+      <c r="K7" s="3">
+        <v>2</v>
+      </c>
+      <c r="L7" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="3">
+        <v>6</v>
+      </c>
+      <c r="C8" s="3">
+        <v>48</v>
+      </c>
+      <c r="D8" s="3">
+        <v>2</v>
+      </c>
+      <c r="E8" s="3">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3">
+        <v>5</v>
+      </c>
+      <c r="I8" s="3">
+        <v>48</v>
+      </c>
+      <c r="J8" s="3">
+        <v>3</v>
+      </c>
+      <c r="K8" s="3">
+        <v>2</v>
+      </c>
+      <c r="L8" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="3">
+        <v>12</v>
+      </c>
+      <c r="C9" s="3">
+        <v>50</v>
+      </c>
+      <c r="D9" s="3">
+        <v>2</v>
+      </c>
+      <c r="E9" s="3">
+        <v>8</v>
+      </c>
+      <c r="F9" s="3">
+        <v>3</v>
+      </c>
+      <c r="G9" s="3">
+        <v>3</v>
+      </c>
+      <c r="H9" s="3">
+        <v>42</v>
+      </c>
+      <c r="I9" s="3">
+        <v>14</v>
+      </c>
+      <c r="J9" s="3">
+        <v>2</v>
+      </c>
+      <c r="K9" s="3">
+        <v>2</v>
+      </c>
+      <c r="L9" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="3">
+        <v>3</v>
+      </c>
+      <c r="C10" s="3">
+        <v>50</v>
+      </c>
+      <c r="D10" s="3">
+        <v>20</v>
+      </c>
+      <c r="E10" s="3">
+        <v>9</v>
+      </c>
+      <c r="F10" s="3">
+        <v>3</v>
+      </c>
+      <c r="G10" s="3">
+        <v>3</v>
+      </c>
+      <c r="H10" s="3">
+        <v>39</v>
+      </c>
+      <c r="I10" s="3">
+        <v>40</v>
+      </c>
+      <c r="J10" s="3">
+        <v>2</v>
+      </c>
+      <c r="K10" s="3">
+        <v>2</v>
+      </c>
+      <c r="L10" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="3">
+        <v>4</v>
+      </c>
+      <c r="C11" s="3">
+        <v>50</v>
+      </c>
+      <c r="D11" s="3">
+        <v>3</v>
+      </c>
+      <c r="E11" s="3">
+        <v>10</v>
+      </c>
+      <c r="F11" s="3">
+        <v>3</v>
+      </c>
+      <c r="G11" s="3">
+        <v>3</v>
+      </c>
+      <c r="H11" s="3">
+        <v>4</v>
+      </c>
+      <c r="I11" s="3">
+        <v>41</v>
+      </c>
+      <c r="J11" s="3">
+        <v>3</v>
+      </c>
+      <c r="K11" s="3">
+        <v>2</v>
+      </c>
+      <c r="L11" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="3">
+        <v>3</v>
+      </c>
+      <c r="C12" s="3">
+        <v>50</v>
+      </c>
+      <c r="D12" s="3">
+        <v>2</v>
+      </c>
+      <c r="E12" s="3">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
+        <v>3</v>
+      </c>
+      <c r="G12" s="3">
+        <v>3</v>
+      </c>
+      <c r="H12" s="3">
+        <v>42</v>
+      </c>
+      <c r="I12" s="3">
+        <v>37</v>
+      </c>
+      <c r="J12" s="3">
+        <v>3</v>
+      </c>
+      <c r="K12" s="3">
+        <v>3</v>
+      </c>
+      <c r="L12" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="3">
+        <v>6</v>
+      </c>
+      <c r="C13" s="3">
+        <v>50</v>
+      </c>
+      <c r="D13" s="3">
+        <v>2</v>
+      </c>
+      <c r="E13" s="3">
+        <v>4</v>
+      </c>
+      <c r="F13" s="3">
+        <v>3</v>
+      </c>
+      <c r="G13" s="3">
+        <v>4</v>
+      </c>
+      <c r="H13" s="3">
+        <v>44</v>
+      </c>
+      <c r="I13" s="3">
+        <v>40</v>
+      </c>
+      <c r="J13" s="3">
+        <v>2</v>
+      </c>
+      <c r="K13" s="3">
+        <v>2</v>
+      </c>
+      <c r="L13" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="3">
+        <v>4</v>
+      </c>
+      <c r="C14" s="3">
+        <v>50</v>
+      </c>
+      <c r="D14" s="3">
+        <v>2</v>
+      </c>
+      <c r="E14" s="3">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
+        <v>16</v>
+      </c>
+      <c r="I14" s="3">
+        <v>16</v>
+      </c>
+      <c r="J14" s="3">
+        <v>2</v>
+      </c>
+      <c r="K14" s="3">
+        <v>2</v>
+      </c>
+      <c r="L14" s="3">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/r_test/plot_metrics/Plot_Metrics_Combined.xlsx
+++ b/r_test/plot_metrics/Plot_Metrics_Combined.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/patrickangst/Documents/GitHub/UWW200_Master_Thesis_public/r_test/plot_metrics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68301C40-8AA5-9E47-A5F1-89242CE0B930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C050DA22-69A6-9F48-A222-349598546CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20580" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38540" yWindow="660" windowWidth="18980" windowHeight="20780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -740,7 +740,7 @@
         <v>26</v>
       </c>
       <c r="O2">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="P2">
         <v>35</v>
@@ -826,7 +826,7 @@
         <v>12</v>
       </c>
       <c r="O3">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="P3">
         <v>13</v>
@@ -912,7 +912,7 @@
         <v>43</v>
       </c>
       <c r="O4">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="P4">
         <v>45</v>
@@ -998,7 +998,7 @@
         <v>40</v>
       </c>
       <c r="O5">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="P5">
         <v>12</v>
@@ -1084,7 +1084,7 @@
         <v>25</v>
       </c>
       <c r="O6">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="P6">
         <v>24</v>
@@ -1170,7 +1170,7 @@
         <v>27</v>
       </c>
       <c r="O7">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="P7">
         <v>13</v>
@@ -1256,7 +1256,7 @@
         <v>11</v>
       </c>
       <c r="O8">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="P8">
         <v>9</v>
@@ -1342,7 +1342,7 @@
         <v>27</v>
       </c>
       <c r="O9">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="P9">
         <v>5</v>
@@ -1428,7 +1428,7 @@
         <v>7</v>
       </c>
       <c r="O10">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="P10">
         <v>34</v>
@@ -1514,7 +1514,7 @@
         <v>48</v>
       </c>
       <c r="O11">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="P11">
         <v>21</v>
@@ -1600,7 +1600,7 @@
         <v>5</v>
       </c>
       <c r="O12">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="P12">
         <v>13</v>
@@ -1686,7 +1686,7 @@
         <v>7</v>
       </c>
       <c r="O13">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="P13">
         <v>24</v>
@@ -1772,7 +1772,7 @@
         <v>42</v>
       </c>
       <c r="O14">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="P14">
         <v>10</v>
@@ -1873,7 +1873,7 @@
         <v>43</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="G2">
         <v>45</v>
@@ -1896,7 +1896,7 @@
         <v>40</v>
       </c>
       <c r="F3">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G3">
         <v>12</v>
@@ -1919,7 +1919,7 @@
         <v>25</v>
       </c>
       <c r="F4">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="G4">
         <v>24</v>
@@ -1942,7 +1942,7 @@
         <v>27</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="G5">
         <v>13</v>
@@ -1965,7 +1965,7 @@
         <v>11</v>
       </c>
       <c r="F6">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G6">
         <v>9</v>
@@ -1988,7 +1988,7 @@
         <v>27</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -2011,7 +2011,7 @@
         <v>48</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="G8">
         <v>21</v>
@@ -2034,7 +2034,7 @@
         <v>5</v>
       </c>
       <c r="F9">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G9">
         <v>13</v>
@@ -2057,7 +2057,7 @@
         <v>7</v>
       </c>
       <c r="F10">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G10">
         <v>24</v>
@@ -2080,7 +2080,7 @@
         <v>42</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="G11">
         <v>10</v>
@@ -2145,7 +2145,7 @@
         <v>26</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="G2">
         <v>35</v>
@@ -2168,7 +2168,7 @@
         <v>12</v>
       </c>
       <c r="F3">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="G3">
         <v>13</v>
@@ -2191,7 +2191,7 @@
         <v>7</v>
       </c>
       <c r="F4">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="G4">
         <v>34</v>
